--- a/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_30_35.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_30_35.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2557169.280679204</v>
+        <v>2557181.517862375</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50121200.11224228</v>
+        <v>50121200.11224227</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -666,7 +666,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>2.454859724202151</v>
@@ -708,19 +708,19 @@
         <v>65.16716277719729</v>
       </c>
       <c r="T2" t="n">
+        <v>98.41444095331364</v>
+      </c>
+      <c r="U2" t="n">
         <v>166</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
-        <v>9.5241252008763</v>
+        <v>166</v>
       </c>
       <c r="W2" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -942,22 +942,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>65.16716277719726</v>
+        <v>32.44050759299143</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>166</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
-        <v>153.0970082705073</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>29.04584091074662</v>
       </c>
       <c r="N7" t="n">
         <v>81.77700969791438</v>
@@ -1091,13 +1091,13 @@
         <v>157.8627444068838</v>
       </c>
       <c r="P7" t="n">
-        <v>72.57304589520173</v>
+        <v>166</v>
       </c>
       <c r="Q7" t="n">
         <v>166</v>
       </c>
       <c r="R7" t="n">
-        <v>166</v>
+        <v>43.5272049844551</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.524125200876329</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1182,16 +1182,16 @@
         <v>65.16716277719729</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="U8" t="n">
         <v>166</v>
       </c>
       <c r="V8" t="n">
-        <v>166</v>
+        <v>93.52481224530183</v>
       </c>
       <c r="W8" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1371,19 +1371,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>139.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>133.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>12.32317129198813</v>
+        <v>123.6703019196078</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,25 +1416,25 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
+        <v>49.2033423405424</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>166</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>166</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>166</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1450,19 +1450,19 @@
         <v>90.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>76.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>52.02011032608413</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>54.04263021464999</v>
       </c>
       <c r="H12" t="n">
-        <v>54.43744567698718</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>128.5629817614496</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>129.1645107035829</v>
@@ -1556,22 +1556,22 @@
         <v>65.68375930532017</v>
       </c>
       <c r="M13" t="n">
-        <v>158.0458409107466</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="P13" t="n">
-        <v>7.291818441733422</v>
+        <v>166</v>
       </c>
       <c r="Q13" t="n">
-        <v>166</v>
+        <v>165.3376593524801</v>
       </c>
       <c r="R13" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>81.19138134219969</v>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>110.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70648148295286</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,16 +1653,16 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>165.1671627771973</v>
+        <v>146.2127999999999</v>
       </c>
       <c r="T14" t="n">
         <v>166</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>84.55655664632661</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>41.51930838617654</v>
       </c>
       <c r="D15" t="n">
         <v>47.93768689770263</v>
@@ -1693,10 +1693,10 @@
         <v>42.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>39.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>25.04263021464999</v>
       </c>
       <c r="H15" t="n">
         <v>25.43744567698717</v>
@@ -1738,19 +1738,19 @@
         <v>102.5487463495893</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>100.164510703583</v>
       </c>
       <c r="V15" t="n">
-        <v>114.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>106.6868605705739</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>119.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>99.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1793,22 +1793,22 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>129.0458409107466</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>166</v>
+        <v>94.0214186578003</v>
       </c>
       <c r="P16" t="n">
         <v>166</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="R16" t="n">
-        <v>130.9755777470537</v>
+        <v>166</v>
       </c>
       <c r="S16" t="n">
         <v>52.1913813421997</v>
@@ -1839,13 +1839,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>180.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>148.4745782429939</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>12.83170880143157</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1890,16 +1890,16 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>164.1671627771973</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
         <v>182</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
       <c r="V17" t="n">
-        <v>178.1384372228027</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>83.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>60.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>46.93768689770263</v>
@@ -1933,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>24.04263021464999</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>24.43744567698717</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>152.6192829834792</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>101.5487463495893</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>99.16451070358298</v>
@@ -1981,13 +1981,13 @@
         <v>113.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>19.67259100492658</v>
       </c>
       <c r="X18" t="n">
         <v>118.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.9472389921755</v>
+        <v>98.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2030,25 +2030,25 @@
         <v>35.68375930532015</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>128.0458409107466</v>
       </c>
       <c r="N19" t="n">
         <v>180.7770096979144</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="P19" t="n">
-        <v>74.65344965456569</v>
+        <v>179.7989900860189</v>
       </c>
       <c r="Q19" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>51.1913813421997</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2082,16 +2082,16 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>109.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>103.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>101.4548597242022</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>10.74037739767614</v>
+        <v>10.74037739767634</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2130,22 +2130,22 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>202.000000000002</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>202.0000000000014</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>198.9222870444234</v>
       </c>
       <c r="Y20" t="n">
-        <v>86.76498197350287</v>
+        <v>202.0000000000009</v>
       </c>
     </row>
     <row r="21">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>83.55655664632661</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>60.09991244551929</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>46.93768689770263</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>41.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>152.6192829834793</v>
       </c>
       <c r="T21" t="n">
         <v>101.5487463495893</v>
@@ -2221,10 +2221,10 @@
         <v>131.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>7.666886867883576</v>
+        <v>118.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>98.39139276613435</v>
+        <v>66.84251041661251</v>
       </c>
     </row>
     <row r="22">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>35.68375930532017</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2273,13 +2273,13 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>126.7302186577975</v>
+        <v>91.04645935248016</v>
       </c>
       <c r="P22" t="n">
-        <v>202.0000000000015</v>
+        <v>202.0000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>202.0000000000011</v>
+        <v>202.0000000000001</v>
       </c>
       <c r="R22" t="n">
         <v>202.0000000000001</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>179.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2325,13 +2325,13 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>102.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>92.67030191960782</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2367,19 +2367,19 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>206.000000000002</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>11.88555641680318</v>
+        <v>206.0000000000014</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>206.0000000000009</v>
       </c>
       <c r="W23" t="n">
-        <v>206.0000000000008</v>
+        <v>181.4447999999974</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>206.0000000000005</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2404,13 +2404,13 @@
         <v>40.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>37.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>23.04263021464999</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>23.43744567698717</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,28 +2440,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>202.0045142735113</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>100.5487463495893</v>
       </c>
       <c r="U24" t="n">
         <v>98.16451070358298</v>
       </c>
       <c r="V24" t="n">
-        <v>112.5106671915202</v>
+        <v>96.13746950898093</v>
       </c>
       <c r="W24" t="n">
-        <v>17.59348495988697</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>117.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>97.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2516,13 +2516,13 @@
         <v>206.0000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.207577747053697</v>
+        <v>54.39895908925342</v>
       </c>
       <c r="R25" t="n">
         <v>206.0000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>50.1913813421997</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>166.0000000000013</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>166.0000000000014</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>155.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>149.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>35.74848261634016</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>147.4548597242022</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>139.6703019196078</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2583,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>60.55231859709119</v>
+        <v>63.81285701765917</v>
       </c>
       <c r="N26" t="n">
-        <v>3.260538420568004</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2616,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>162.8495103931286</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>8.674882659508297</v>
+        <v>166.0000000000019</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>166.0000000000016</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>145.164510703583</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>159.5106671915202</v>
+        <v>1.821407233861333</v>
       </c>
       <c r="W27" t="n">
-        <v>166.000000000001</v>
+        <v>166.0000000000008</v>
       </c>
       <c r="X27" t="n">
-        <v>164.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>144.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2714,10 +2714,10 @@
         <v>17.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>30.53621805555548</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>25.98090483695654</v>
       </c>
       <c r="F28" t="n">
         <v>19.38285596774193</v>
@@ -2741,16 +2741,16 @@
         <v>81.68375930532015</v>
       </c>
       <c r="M28" t="n">
-        <v>166.0000000000016</v>
+        <v>166</v>
       </c>
       <c r="N28" t="n">
-        <v>87.33534772122334</v>
+        <v>67.16149063705271</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>166.0000000000019</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>97.1913813421997</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>32.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -2799,13 +2799,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>91.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>89.45485972420214</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>81.67030191960782</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>154.9442062929542</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>70.83913538953659</v>
       </c>
     </row>
     <row r="30">
@@ -2866,16 +2866,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>71.55655664632661</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>48.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>34.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>29.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>26.63624233787687</v>
@@ -2914,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>124.9722187371841</v>
       </c>
       <c r="S30" t="n">
-        <v>46.17084830220659</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>89.54874634958929</v>
@@ -2929,10 +2929,10 @@
         <v>101.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>119.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>106.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>23.68375930532015</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>116.0458409107466</v>
@@ -2987,13 +2987,13 @@
         <v>166</v>
       </c>
       <c r="P31" t="n">
-        <v>6.483199783933156</v>
+        <v>166</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>30.1669590892533</v>
       </c>
       <c r="R31" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3030,19 +3030,19 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>85.33915573984979</v>
       </c>
       <c r="E32" t="n">
         <v>79.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>79.88962870801186</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>69.67030191960782</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3081,19 +3081,19 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>166.0000000000013</v>
+        <v>166.0000000000011</v>
       </c>
       <c r="V32" t="n">
-        <v>66.84951039312848</v>
+        <v>163.9504240256607</v>
       </c>
       <c r="W32" t="n">
-        <v>166.0000000000007</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>166.0000000000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3106,22 +3106,22 @@
         <v>59.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>36.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>22.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>17.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>14.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04263021464998462</v>
+        <v>0.04263021464998928</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4374456769871689</v>
+        <v>0.4374456769871813</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>166.0000000000007</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -3160,16 +3160,16 @@
         <v>77.54874634958929</v>
       </c>
       <c r="U33" t="n">
-        <v>75.16451070358298</v>
+        <v>75.16451070358295</v>
       </c>
       <c r="V33" t="n">
         <v>89.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>101.5608504512086</v>
+        <v>81.35217210281047</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>94.86273944538755</v>
       </c>
       <c r="Y33" t="n">
         <v>74.39139276613435</v>
@@ -3212,28 +3212,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>11.68375930532017</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>146.212799999997</v>
+        <v>156.7770096979144</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>166.0000000000012</v>
+        <v>116.5606496545647</v>
       </c>
       <c r="Q34" t="n">
         <v>166.000000000001</v>
       </c>
       <c r="R34" t="n">
-        <v>166.0000000000008</v>
+        <v>166</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>27.19138134219969</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>79.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>77.45485972420215</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>69.67030191960782</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3312,22 +3312,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>140.1671627771973</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>166.0000000000012</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>166.0000000000013</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>166.0000000000003</v>
       </c>
       <c r="W35" t="n">
-        <v>15.22748789172934</v>
+        <v>166.0000000000002</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>165.0876383561895</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3346,10 +3346,10 @@
         <v>36.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>22.93768689770263</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>17.67209722191262</v>
       </c>
       <c r="F36" t="n">
         <v>14.63624233787687</v>
@@ -3391,22 +3391,22 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>128.6192829834793</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>77.54874634958929</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>75.16451070358295</v>
       </c>
       <c r="V36" t="n">
         <v>89.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>107.3731429098285</v>
+        <v>104.2898590005131</v>
       </c>
       <c r="X36" t="n">
-        <v>33.05909358038575</v>
+        <v>94.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>74.39139276613435</v>
@@ -3455,22 +3455,22 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>107.3376593524769</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
+        <v>134.5290406946778</v>
+      </c>
+      <c r="P37" t="n">
         <v>166.000000000001</v>
       </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
       <c r="Q37" t="n">
-        <v>166.0000000000015</v>
+        <v>166.000000000001</v>
       </c>
       <c r="R37" t="n">
-        <v>166.0000000000008</v>
+        <v>166</v>
       </c>
       <c r="S37" t="n">
-        <v>27.19138134219969</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3507,16 +3507,16 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>80.36328960686865</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>80.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>78.45485972420215</v>
+        <v>78.45485972420214</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>70.67030191960782</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3531,10 +3531,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>63.81285701765917</v>
       </c>
       <c r="N38" t="n">
-        <v>63.81285701765917</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3555,19 +3555,19 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>50.36082884274106</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>116.2840490772288</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>166.0000000000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3577,25 +3577,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>60.55655664632661</v>
       </c>
       <c r="C39" t="n">
         <v>37.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>23.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>18.67209722191262</v>
       </c>
       <c r="F39" t="n">
         <v>15.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1.042630214649985</v>
       </c>
       <c r="H39" t="n">
-        <v>1.437445676987181</v>
+        <v>1.437445676987169</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,25 +3625,25 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>166.0000000000012</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>103.4238825287886</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>78.54874634958929</v>
       </c>
       <c r="U39" t="n">
-        <v>76.16451070358295</v>
+        <v>76.16451070358298</v>
       </c>
       <c r="V39" t="n">
         <v>90.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>108.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>56.84176863836948</v>
       </c>
       <c r="Y39" t="n">
         <v>75.39139276613435</v>
@@ -3686,28 +3686,28 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>12.68375930532017</v>
+        <v>12.68375930532015</v>
       </c>
       <c r="M40" t="n">
         <v>105.0458409107466</v>
       </c>
       <c r="N40" t="n">
-        <v>0.2918184417298471</v>
+        <v>28.48319978393083</v>
       </c>
       <c r="O40" t="n">
         <v>166.0000000000012</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>166.0000000000012</v>
       </c>
       <c r="Q40" t="n">
-        <v>166.0000000000015</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>166.000000000001</v>
+        <v>166</v>
       </c>
       <c r="S40" t="n">
-        <v>28.19138134219969</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,22 +3735,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>150.0000000000005</v>
       </c>
       <c r="C41" t="n">
-        <v>150</v>
+        <v>63.06035594557262</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>150.0000000000001</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>63.06035594557487</v>
+        <v>150.0000000000017</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3768,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>79.17009580559889</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>69.05964405442512</v>
       </c>
       <c r="S41" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>132.12</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>93.13204626870701</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3865,19 +3865,19 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="T42" t="n">
-        <v>150</v>
+        <v>150.0000000000011</v>
       </c>
       <c r="U42" t="n">
-        <v>150</v>
+        <v>150.0000000000013</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>38.98795373129055</v>
       </c>
       <c r="W42" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>103.9282313574022</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>103.9282313574022</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3978,16 +3978,16 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>27.63795589520483</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4020,13 +4020,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>27.63795589520483</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4035,10 +4035,10 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,22 +4099,22 @@
         <v>71.11986886406447</v>
       </c>
       <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>43.38413113593551</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
         <v>130</v>
-      </c>
-      <c r="S45" t="n">
-        <v>130</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>130</v>
-      </c>
-      <c r="W45" t="n">
-        <v>43.38413113593555</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>18.65953135740219</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>18.65953135740219</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85.52395153729935</v>
+        <v>80.58493264031769</v>
       </c>
       <c r="C2" t="n">
-        <v>35.54963007972975</v>
+        <v>30.61061118274807</v>
       </c>
       <c r="D2" t="n">
-        <v>25.10603842331582</v>
+        <v>20.16701952633414</v>
       </c>
       <c r="E2" t="n">
-        <v>20.69867518405455</v>
+        <v>15.75965628707288</v>
       </c>
       <c r="F2" t="n">
         <v>15.75965628707288</v>
@@ -4351,22 +4351,22 @@
         <v>598.1745830533361</v>
       </c>
       <c r="T2" t="n">
-        <v>430.4978153765684</v>
+        <v>498.7660568378677</v>
       </c>
       <c r="U2" t="n">
-        <v>430.4978153765684</v>
+        <v>331.0892891611001</v>
       </c>
       <c r="V2" t="n">
-        <v>420.8774868908347</v>
+        <v>163.4125214843323</v>
       </c>
       <c r="W2" t="n">
-        <v>253.200719214067</v>
+        <v>163.4125214843323</v>
       </c>
       <c r="X2" t="n">
-        <v>85.52395153729935</v>
+        <v>163.4125214843323</v>
       </c>
       <c r="Y2" t="n">
-        <v>85.52395153729935</v>
+        <v>163.4125214843323</v>
       </c>
     </row>
     <row r="3">
@@ -4412,7 +4412,7 @@
         <v>57.90702557396233</v>
       </c>
       <c r="N3" t="n">
-        <v>57.90702557396233</v>
+        <v>190.9986670150445</v>
       </c>
       <c r="O3" t="n">
         <v>215.3396069424725</v>
@@ -4455,22 +4455,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>224.9505324712223</v>
+        <v>664</v>
       </c>
       <c r="C4" t="n">
-        <v>224.9505324712223</v>
+        <v>664</v>
       </c>
       <c r="D4" t="n">
-        <v>224.9505324712223</v>
+        <v>664</v>
       </c>
       <c r="E4" t="n">
-        <v>342.7794366826353</v>
+        <v>664</v>
       </c>
       <c r="F4" t="n">
-        <v>467.1404092745708</v>
+        <v>664</v>
       </c>
       <c r="G4" t="n">
-        <v>621.1253948335873</v>
+        <v>664</v>
       </c>
       <c r="H4" t="n">
         <v>664</v>
@@ -4509,22 +4509,22 @@
         <v>60.61053247122231</v>
       </c>
       <c r="T4" t="n">
-        <v>60.61053247122231</v>
+        <v>224.9505324712223</v>
       </c>
       <c r="U4" t="n">
-        <v>60.61053247122231</v>
+        <v>389.2905324712223</v>
       </c>
       <c r="V4" t="n">
-        <v>224.9505324712223</v>
+        <v>553.6305324712223</v>
       </c>
       <c r="W4" t="n">
-        <v>224.9505324712223</v>
+        <v>553.6305324712223</v>
       </c>
       <c r="X4" t="n">
-        <v>224.9505324712223</v>
+        <v>664</v>
       </c>
       <c r="Y4" t="n">
-        <v>224.9505324712223</v>
+        <v>664</v>
       </c>
     </row>
     <row r="5">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.58493264031767</v>
+        <v>15.75965628707287</v>
       </c>
       <c r="C5" t="n">
-        <v>30.61061118274806</v>
+        <v>15.75965628707287</v>
       </c>
       <c r="D5" t="n">
-        <v>20.16701952633413</v>
+        <v>15.75965628707287</v>
       </c>
       <c r="E5" t="n">
         <v>15.75965628707287</v>
@@ -4585,25 +4585,25 @@
         <v>664</v>
       </c>
       <c r="S5" t="n">
-        <v>598.1745830533361</v>
+        <v>631.2318105121299</v>
       </c>
       <c r="T5" t="n">
-        <v>598.1745830533361</v>
+        <v>463.5550428353622</v>
       </c>
       <c r="U5" t="n">
-        <v>430.4978153765684</v>
+        <v>463.5550428353622</v>
       </c>
       <c r="V5" t="n">
-        <v>430.4978153765684</v>
+        <v>295.8782751585945</v>
       </c>
       <c r="W5" t="n">
-        <v>275.8543726790863</v>
+        <v>295.8782751585945</v>
       </c>
       <c r="X5" t="n">
-        <v>275.8543726790863</v>
+        <v>128.2015074818268</v>
       </c>
       <c r="Y5" t="n">
-        <v>163.4125214843323</v>
+        <v>15.75965628707287</v>
       </c>
     </row>
     <row r="6">
@@ -4637,22 +4637,22 @@
         <v>13.28</v>
       </c>
       <c r="J6" t="n">
-        <v>13.28</v>
+        <v>146.3716414410821</v>
       </c>
       <c r="K6" t="n">
-        <v>20.96100896075475</v>
+        <v>154.0526504018368</v>
       </c>
       <c r="L6" t="n">
-        <v>57.90702557396233</v>
+        <v>190.9986670150444</v>
       </c>
       <c r="M6" t="n">
-        <v>57.90702557396233</v>
+        <v>190.9986670150444</v>
       </c>
       <c r="N6" t="n">
-        <v>57.90702557396233</v>
+        <v>190.9986670150444</v>
       </c>
       <c r="O6" t="n">
-        <v>82.24796550139034</v>
+        <v>215.3396069424724</v>
       </c>
       <c r="P6" t="n">
         <v>242.6573776332314</v>
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>448.1171708165467</v>
+        <v>125.0373376662921</v>
       </c>
       <c r="C7" t="n">
-        <v>448.1171708165467</v>
+        <v>251.0393434847279</v>
       </c>
       <c r="D7" t="n">
-        <v>448.1171708165467</v>
+        <v>364.358487609728</v>
       </c>
       <c r="E7" t="n">
-        <v>448.1171708165467</v>
+        <v>482.187391821141</v>
       </c>
       <c r="F7" t="n">
-        <v>572.4781434084822</v>
+        <v>482.187391821141</v>
       </c>
       <c r="G7" t="n">
-        <v>572.4781434084822</v>
+        <v>482.187391821141</v>
       </c>
       <c r="H7" t="n">
-        <v>572.4781434084822</v>
+        <v>482.187391821141</v>
       </c>
       <c r="I7" t="n">
-        <v>572.4781434084822</v>
+        <v>482.187391821141</v>
       </c>
       <c r="J7" t="n">
-        <v>601.316921712267</v>
+        <v>646.527391821141</v>
       </c>
       <c r="K7" t="n">
-        <v>601.316921712267</v>
+        <v>646.527391821141</v>
       </c>
       <c r="L7" t="n">
         <v>664</v>
       </c>
       <c r="M7" t="n">
-        <v>664</v>
+        <v>634.6607667568215</v>
       </c>
       <c r="N7" t="n">
-        <v>581.3969599010966</v>
+        <v>552.0577266579181</v>
       </c>
       <c r="O7" t="n">
-        <v>421.9396423183857</v>
+        <v>392.6004090752072</v>
       </c>
       <c r="P7" t="n">
-        <v>348.6335353535354</v>
+        <v>224.9236413984395</v>
       </c>
       <c r="Q7" t="n">
-        <v>180.9567676767677</v>
+        <v>57.24687372167182</v>
       </c>
       <c r="R7" t="n">
         <v>13.28</v>
       </c>
       <c r="S7" t="n">
-        <v>60.61053247122229</v>
+        <v>13.28</v>
       </c>
       <c r="T7" t="n">
-        <v>60.61053247122229</v>
+        <v>13.28</v>
       </c>
       <c r="U7" t="n">
-        <v>60.61053247122229</v>
+        <v>13.28</v>
       </c>
       <c r="V7" t="n">
-        <v>60.61053247122229</v>
+        <v>13.28</v>
       </c>
       <c r="W7" t="n">
-        <v>224.9505324712223</v>
+        <v>13.28</v>
       </c>
       <c r="X7" t="n">
-        <v>224.9505324712223</v>
+        <v>13.28</v>
       </c>
       <c r="Y7" t="n">
-        <v>336.3598331502545</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="8">
@@ -4825,22 +4825,22 @@
         <v>598.1745830533361</v>
       </c>
       <c r="T8" t="n">
-        <v>598.1745830533361</v>
+        <v>430.4978153765684</v>
       </c>
       <c r="U8" t="n">
-        <v>430.4978153765684</v>
+        <v>262.8210476998007</v>
       </c>
       <c r="V8" t="n">
-        <v>262.8210476998007</v>
+        <v>168.351540381314</v>
       </c>
       <c r="W8" t="n">
-        <v>95.14428002303302</v>
+        <v>168.351540381314</v>
       </c>
       <c r="X8" t="n">
-        <v>95.14428002303302</v>
+        <v>168.351540381314</v>
       </c>
       <c r="Y8" t="n">
-        <v>95.14428002303302</v>
+        <v>168.351540381314</v>
       </c>
     </row>
     <row r="9">
@@ -4886,7 +4886,7 @@
         <v>57.90702557396233</v>
       </c>
       <c r="N9" t="n">
-        <v>57.90702557396233</v>
+        <v>190.9986670150445</v>
       </c>
       <c r="O9" t="n">
         <v>215.3396069424725</v>
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>211.6413234954158</v>
+        <v>361.9957717688311</v>
       </c>
       <c r="C10" t="n">
-        <v>211.6413234954158</v>
+        <v>487.9977775872669</v>
       </c>
       <c r="D10" t="n">
-        <v>217.4910957885869</v>
+        <v>601.316921712267</v>
       </c>
       <c r="E10" t="n">
-        <v>335.3199999999999</v>
+        <v>601.316921712267</v>
       </c>
       <c r="F10" t="n">
-        <v>335.3199999999999</v>
+        <v>601.316921712267</v>
       </c>
       <c r="G10" t="n">
-        <v>335.3199999999999</v>
+        <v>601.316921712267</v>
       </c>
       <c r="H10" t="n">
-        <v>335.3199999999999</v>
+        <v>601.316921712267</v>
       </c>
       <c r="I10" t="n">
-        <v>499.66</v>
+        <v>601.316921712267</v>
       </c>
       <c r="J10" t="n">
-        <v>499.66</v>
+        <v>601.316921712267</v>
       </c>
       <c r="K10" t="n">
-        <v>664</v>
+        <v>601.316921712267</v>
       </c>
       <c r="L10" t="n">
         <v>664</v>
@@ -4989,16 +4989,16 @@
         <v>60.61053247122231</v>
       </c>
       <c r="V10" t="n">
-        <v>60.61053247122231</v>
+        <v>85.89843410253897</v>
       </c>
       <c r="W10" t="n">
-        <v>60.61053247122231</v>
+        <v>250.238434102539</v>
       </c>
       <c r="X10" t="n">
-        <v>211.6413234954158</v>
+        <v>250.238434102539</v>
       </c>
       <c r="Y10" t="n">
-        <v>211.6413234954158</v>
+        <v>250.238434102539</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>160.969696969697</v>
+        <v>278.946118847937</v>
       </c>
       <c r="C11" t="n">
-        <v>160.969696969697</v>
+        <v>278.946118847937</v>
       </c>
       <c r="D11" t="n">
-        <v>160.969696969697</v>
+        <v>138.1994968884928</v>
       </c>
       <c r="E11" t="n">
-        <v>160.969696969697</v>
+        <v>138.1994968884928</v>
       </c>
       <c r="F11" t="n">
-        <v>25.72764776968498</v>
+        <v>138.1994968884928</v>
       </c>
       <c r="G11" t="n">
-        <v>25.72764776968498</v>
+        <v>138.1994968884928</v>
       </c>
       <c r="H11" t="n">
         <v>13.28</v>
@@ -5059,25 +5059,25 @@
         <v>664</v>
       </c>
       <c r="S11" t="n">
-        <v>496.3232323232323</v>
+        <v>614.2996542014723</v>
       </c>
       <c r="T11" t="n">
-        <v>496.3232323232323</v>
+        <v>614.2996542014723</v>
       </c>
       <c r="U11" t="n">
-        <v>496.3232323232323</v>
+        <v>446.6228865247047</v>
       </c>
       <c r="V11" t="n">
-        <v>328.6464646464647</v>
+        <v>446.6228865247047</v>
       </c>
       <c r="W11" t="n">
-        <v>328.6464646464647</v>
+        <v>446.6228865247047</v>
       </c>
       <c r="X11" t="n">
-        <v>160.969696969697</v>
+        <v>446.6228865247047</v>
       </c>
       <c r="Y11" t="n">
-        <v>160.969696969697</v>
+        <v>278.946118847937</v>
       </c>
     </row>
     <row r="12">
@@ -5087,43 +5087,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>159.2773314368752</v>
+        <v>289.1389291757132</v>
       </c>
       <c r="C12" t="n">
-        <v>68.26731886564363</v>
+        <v>198.1289166044816</v>
       </c>
       <c r="D12" t="n">
-        <v>68.26731886564363</v>
+        <v>120.4140813542769</v>
       </c>
       <c r="E12" t="n">
-        <v>68.26731886564363</v>
+        <v>67.86851536833333</v>
       </c>
       <c r="F12" t="n">
-        <v>68.26731886564363</v>
+        <v>67.86851536833333</v>
       </c>
       <c r="G12" t="n">
-        <v>68.26731886564363</v>
+        <v>13.28</v>
       </c>
       <c r="H12" t="n">
         <v>13.28</v>
       </c>
       <c r="I12" t="n">
-        <v>13.28</v>
+        <v>72.81896812037627</v>
       </c>
       <c r="J12" t="n">
-        <v>13.28</v>
+        <v>237.1589681203763</v>
       </c>
       <c r="K12" t="n">
-        <v>177.62</v>
+        <v>248.3915488455078</v>
       </c>
       <c r="L12" t="n">
-        <v>308.002229309241</v>
+        <v>285.3375654587154</v>
       </c>
       <c r="M12" t="n">
-        <v>308.002229309241</v>
+        <v>347.5444349757683</v>
       </c>
       <c r="N12" t="n">
-        <v>308.002229309241</v>
+        <v>448.001289381813</v>
       </c>
       <c r="O12" t="n">
         <v>472.342229309241</v>
@@ -5141,22 +5141,22 @@
         <v>664</v>
       </c>
       <c r="T12" t="n">
-        <v>534.138402261162</v>
+        <v>664</v>
       </c>
       <c r="U12" t="n">
-        <v>403.6691995302701</v>
+        <v>533.5307972691081</v>
       </c>
       <c r="V12" t="n">
-        <v>403.6691995302701</v>
+        <v>533.5307972691081</v>
       </c>
       <c r="W12" t="n">
-        <v>403.6691995302701</v>
+        <v>533.5307972691081</v>
       </c>
       <c r="X12" t="n">
-        <v>403.6691995302701</v>
+        <v>533.5307972691081</v>
       </c>
       <c r="Y12" t="n">
-        <v>273.9809240089223</v>
+        <v>403.8425217477603</v>
       </c>
     </row>
     <row r="13">
@@ -5199,19 +5199,19 @@
         <v>597.6527683784644</v>
       </c>
       <c r="M13" t="n">
-        <v>438.0105048322557</v>
+        <v>597.6527683784644</v>
       </c>
       <c r="N13" t="n">
-        <v>438.0105048322557</v>
+        <v>597.6527683784644</v>
       </c>
       <c r="O13" t="n">
-        <v>438.0105048322557</v>
+        <v>429.9760007016968</v>
       </c>
       <c r="P13" t="n">
-        <v>430.6450316587876</v>
+        <v>262.2992330249291</v>
       </c>
       <c r="Q13" t="n">
-        <v>262.9682639820199</v>
+        <v>95.29149630525222</v>
       </c>
       <c r="R13" t="n">
         <v>95.29149630525222</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>161.8109466896996</v>
+        <v>13.28</v>
       </c>
       <c r="C14" t="n">
-        <v>161.8109466896996</v>
+        <v>13.28</v>
       </c>
       <c r="D14" t="n">
-        <v>50.35725402318471</v>
+        <v>13.28</v>
       </c>
       <c r="E14" t="n">
-        <v>50.35725402318471</v>
+        <v>13.28</v>
       </c>
       <c r="F14" t="n">
-        <v>50.35725402318471</v>
+        <v>13.28</v>
       </c>
       <c r="G14" t="n">
-        <v>50.35725402318471</v>
+        <v>13.28</v>
       </c>
       <c r="H14" t="n">
         <v>13.28</v>
@@ -5296,25 +5296,25 @@
         <v>664</v>
       </c>
       <c r="S14" t="n">
-        <v>497.1644820432351</v>
+        <v>516.3103030303031</v>
       </c>
       <c r="T14" t="n">
-        <v>329.4877143664673</v>
+        <v>348.6335353535354</v>
       </c>
       <c r="U14" t="n">
-        <v>329.4877143664673</v>
+        <v>180.9567676767677</v>
       </c>
       <c r="V14" t="n">
-        <v>329.4877143664673</v>
+        <v>13.28</v>
       </c>
       <c r="W14" t="n">
-        <v>329.4877143664673</v>
+        <v>13.28</v>
       </c>
       <c r="X14" t="n">
-        <v>329.4877143664673</v>
+        <v>13.28</v>
       </c>
       <c r="Y14" t="n">
-        <v>161.8109466896996</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="15">
@@ -5324,19 +5324,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>130.4994240369722</v>
+        <v>237.7703138740463</v>
       </c>
       <c r="C15" t="n">
-        <v>130.4994240369722</v>
+        <v>195.831618534474</v>
       </c>
       <c r="D15" t="n">
-        <v>82.07751807969677</v>
+        <v>147.4097125771986</v>
       </c>
       <c r="E15" t="n">
-        <v>38.97438957271432</v>
+        <v>104.3065840702162</v>
       </c>
       <c r="F15" t="n">
-        <v>38.97438957271432</v>
+        <v>64.26997564811835</v>
       </c>
       <c r="G15" t="n">
         <v>38.97438957271432</v>
@@ -5345,19 +5345,19 @@
         <v>13.28</v>
       </c>
       <c r="I15" t="n">
-        <v>15.79934317898054</v>
+        <v>101.5289681203763</v>
       </c>
       <c r="J15" t="n">
-        <v>15.79934317898054</v>
+        <v>101.5289681203763</v>
       </c>
       <c r="K15" t="n">
-        <v>180.1393431789805</v>
+        <v>109.209977081131</v>
       </c>
       <c r="L15" t="n">
-        <v>217.0853597921881</v>
+        <v>146.1559936943386</v>
       </c>
       <c r="M15" t="n">
-        <v>308.002229309241</v>
+        <v>178.8353749031963</v>
       </c>
       <c r="N15" t="n">
         <v>308.002229309241</v>
@@ -5381,19 +5381,19 @@
         <v>560.4154077276876</v>
       </c>
       <c r="U15" t="n">
-        <v>560.4154077276876</v>
+        <v>459.239134289725</v>
       </c>
       <c r="V15" t="n">
-        <v>444.7480671301925</v>
+        <v>459.239134289725</v>
       </c>
       <c r="W15" t="n">
-        <v>336.9835615033501</v>
+        <v>459.239134289725</v>
       </c>
       <c r="X15" t="n">
-        <v>215.91008731609</v>
+        <v>338.1656601024648</v>
       </c>
       <c r="Y15" t="n">
-        <v>215.91008731609</v>
+        <v>237.7703138740463</v>
       </c>
     </row>
     <row r="16">
@@ -5403,31 +5403,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>354.7368491821429</v>
+        <v>489.9102913053317</v>
       </c>
       <c r="C16" t="n">
-        <v>381.7388550005786</v>
+        <v>516.9122971237674</v>
       </c>
       <c r="D16" t="n">
-        <v>396.0579991255787</v>
+        <v>516.9122971237674</v>
       </c>
       <c r="E16" t="n">
-        <v>414.8869033369917</v>
+        <v>535.7412013351804</v>
       </c>
       <c r="F16" t="n">
-        <v>440.2478759289272</v>
+        <v>535.7412013351804</v>
       </c>
       <c r="G16" t="n">
-        <v>495.2328614879436</v>
+        <v>590.7261868941969</v>
       </c>
       <c r="H16" t="n">
-        <v>495.2328614879436</v>
+        <v>590.7261868941969</v>
       </c>
       <c r="I16" t="n">
-        <v>495.2328614879436</v>
+        <v>590.7261868941969</v>
       </c>
       <c r="J16" t="n">
-        <v>659.5728614879437</v>
+        <v>590.7261868941969</v>
       </c>
       <c r="K16" t="n">
         <v>664</v>
@@ -5436,19 +5436,19 @@
         <v>664</v>
       </c>
       <c r="M16" t="n">
-        <v>533.6506657467206</v>
+        <v>664</v>
       </c>
       <c r="N16" t="n">
-        <v>533.6506657467206</v>
+        <v>664</v>
       </c>
       <c r="O16" t="n">
-        <v>365.973898069953</v>
+        <v>569.028870042626</v>
       </c>
       <c r="P16" t="n">
-        <v>198.2971303931853</v>
+        <v>401.3521023658583</v>
       </c>
       <c r="Q16" t="n">
-        <v>198.2971303931853</v>
+        <v>233.6753346890906</v>
       </c>
       <c r="R16" t="n">
         <v>65.99856701232294</v>
@@ -5460,19 +5460,19 @@
         <v>104.8271086670016</v>
       </c>
       <c r="U16" t="n">
-        <v>104.8271086670016</v>
+        <v>252.4098514692226</v>
       </c>
       <c r="V16" t="n">
-        <v>204.6485015529476</v>
+        <v>352.2312443551686</v>
       </c>
       <c r="W16" t="n">
-        <v>277.5394198126249</v>
+        <v>425.122162614846</v>
       </c>
       <c r="X16" t="n">
-        <v>329.5702108368185</v>
+        <v>477.1529536390395</v>
       </c>
       <c r="Y16" t="n">
-        <v>341.9795115158507</v>
+        <v>477.1529536390395</v>
       </c>
     </row>
     <row r="17">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14.56</v>
+        <v>177.4956434792177</v>
       </c>
       <c r="C17" t="n">
-        <v>14.56</v>
+        <v>27.52132202164805</v>
       </c>
       <c r="D17" t="n">
         <v>14.56</v>
@@ -5533,25 +5533,25 @@
         <v>728</v>
       </c>
       <c r="S17" t="n">
-        <v>562.1745830533361</v>
+        <v>728</v>
       </c>
       <c r="T17" t="n">
-        <v>378.3361992149522</v>
+        <v>728</v>
       </c>
       <c r="U17" t="n">
-        <v>378.3361992149522</v>
+        <v>544.1616161616162</v>
       </c>
       <c r="V17" t="n">
-        <v>198.3983838383839</v>
+        <v>544.1616161616162</v>
       </c>
       <c r="W17" t="n">
-        <v>198.3983838383839</v>
+        <v>544.1616161616162</v>
       </c>
       <c r="X17" t="n">
-        <v>198.3983838383839</v>
+        <v>544.1616161616162</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.56</v>
+        <v>360.3232323232323</v>
       </c>
     </row>
     <row r="18">
@@ -5561,49 +5561,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>128.3503175093588</v>
+        <v>189.4561032748704</v>
       </c>
       <c r="C18" t="n">
-        <v>128.3503175093588</v>
+        <v>128.7491210066691</v>
       </c>
       <c r="D18" t="n">
-        <v>80.93851256218446</v>
+        <v>81.33731605949474</v>
       </c>
       <c r="E18" t="n">
-        <v>38.84548506530302</v>
+        <v>39.2442885626133</v>
       </c>
       <c r="F18" t="n">
-        <v>38.84548506530302</v>
+        <v>39.2442885626133</v>
       </c>
       <c r="G18" t="n">
-        <v>14.56</v>
+        <v>39.2442885626133</v>
       </c>
       <c r="H18" t="n">
         <v>14.56</v>
       </c>
       <c r="I18" t="n">
-        <v>14.56</v>
+        <v>103.7989681203763</v>
       </c>
       <c r="J18" t="n">
-        <v>14.56</v>
+        <v>283.9789681203763</v>
       </c>
       <c r="K18" t="n">
-        <v>194.74</v>
+        <v>291.659977081131</v>
       </c>
       <c r="L18" t="n">
-        <v>248.4153597921881</v>
+        <v>328.6059936943386</v>
       </c>
       <c r="M18" t="n">
-        <v>340.322229309241</v>
+        <v>420.5128632113915</v>
       </c>
       <c r="N18" t="n">
-        <v>340.322229309241</v>
+        <v>550.6697176174363</v>
       </c>
       <c r="O18" t="n">
-        <v>520.502229309241</v>
+        <v>575.0106575448643</v>
       </c>
       <c r="P18" t="n">
-        <v>547.8199999999999</v>
+        <v>602.3284282356233</v>
       </c>
       <c r="Q18" t="n">
         <v>728</v>
@@ -5612,25 +5612,25 @@
         <v>728</v>
       </c>
       <c r="S18" t="n">
-        <v>573.8391080974957</v>
+        <v>728</v>
       </c>
       <c r="T18" t="n">
-        <v>471.2646168352843</v>
+        <v>728</v>
       </c>
       <c r="U18" t="n">
-        <v>371.0984444074227</v>
+        <v>627.8338275721384</v>
       </c>
       <c r="V18" t="n">
-        <v>256.4412048200286</v>
+        <v>513.1765879847443</v>
       </c>
       <c r="W18" t="n">
-        <v>256.4412048200286</v>
+        <v>493.3052839393639</v>
       </c>
       <c r="X18" t="n">
-        <v>136.3778316428694</v>
+        <v>373.2419107622047</v>
       </c>
       <c r="Y18" t="n">
-        <v>128.3503175093588</v>
+        <v>273.8566655438872</v>
       </c>
     </row>
     <row r="19">
@@ -5640,28 +5640,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>262.4711579652904</v>
+        <v>417.9924833173623</v>
       </c>
       <c r="C19" t="n">
-        <v>262.4711579652904</v>
+        <v>445.9844891357981</v>
       </c>
       <c r="D19" t="n">
-        <v>262.4711579652904</v>
+        <v>445.9844891357981</v>
       </c>
       <c r="E19" t="n">
-        <v>282.2900621767034</v>
+        <v>465.8033933472111</v>
       </c>
       <c r="F19" t="n">
-        <v>282.2900621767034</v>
+        <v>492.1543659391466</v>
       </c>
       <c r="G19" t="n">
-        <v>282.2900621767034</v>
+        <v>548.129351498163</v>
       </c>
       <c r="H19" t="n">
-        <v>358.9393240574125</v>
+        <v>624.778613378872</v>
       </c>
       <c r="I19" t="n">
-        <v>477.3340185469154</v>
+        <v>648.4437168828038</v>
       </c>
       <c r="J19" t="n">
         <v>648.4437168828038</v>
@@ -5673,43 +5673,43 @@
         <v>691.9557986814948</v>
       </c>
       <c r="M19" t="n">
-        <v>691.9557986814948</v>
+        <v>562.6165654383165</v>
       </c>
       <c r="N19" t="n">
-        <v>509.3527585825914</v>
+        <v>380.013525339413</v>
       </c>
       <c r="O19" t="n">
-        <v>509.3527585825914</v>
+        <v>196.1751415010292</v>
       </c>
       <c r="P19" t="n">
-        <v>433.9452336789897</v>
+        <v>14.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>250.1068498406058</v>
+        <v>14.56</v>
       </c>
       <c r="R19" t="n">
-        <v>66.26846600222193</v>
+        <v>14.56</v>
       </c>
       <c r="S19" t="n">
         <v>14.56</v>
       </c>
       <c r="T19" t="n">
-        <v>81.49233570982651</v>
+        <v>14.56</v>
       </c>
       <c r="U19" t="n">
-        <v>81.49233570982651</v>
+        <v>163.1327428022211</v>
       </c>
       <c r="V19" t="n">
-        <v>182.3037285957725</v>
+        <v>263.944135688167</v>
       </c>
       <c r="W19" t="n">
-        <v>182.3037285957725</v>
+        <v>337.8250539478444</v>
       </c>
       <c r="X19" t="n">
-        <v>235.324519619966</v>
+        <v>390.8458449720379</v>
       </c>
       <c r="Y19" t="n">
-        <v>248.7238202989982</v>
+        <v>404.2451456510702</v>
       </c>
     </row>
     <row r="20">
@@ -5719,19 +5719,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>333.4906111827481</v>
+        <v>16.16</v>
       </c>
       <c r="C20" t="n">
-        <v>333.4906111827481</v>
+        <v>16.16</v>
       </c>
       <c r="D20" t="n">
-        <v>223.0470195263342</v>
+        <v>16.16</v>
       </c>
       <c r="E20" t="n">
-        <v>118.6396562870729</v>
+        <v>16.16</v>
       </c>
       <c r="F20" t="n">
-        <v>118.6396562870729</v>
+        <v>16.16</v>
       </c>
       <c r="G20" t="n">
         <v>16.16</v>
@@ -5740,55 +5740,55 @@
         <v>16.16</v>
       </c>
       <c r="I20" t="n">
-        <v>47.22571884093131</v>
+        <v>16.16</v>
       </c>
       <c r="J20" t="n">
-        <v>121.9767770301512</v>
+        <v>90.91105818921989</v>
       </c>
       <c r="K20" t="n">
-        <v>286.0044146180909</v>
+        <v>254.9386957771596</v>
       </c>
       <c r="L20" t="n">
-        <v>485.9844146180909</v>
+        <v>454.9186957771595</v>
       </c>
       <c r="M20" t="n">
-        <v>475.1355485598321</v>
+        <v>444.0698297189007</v>
       </c>
       <c r="N20" t="n">
-        <v>475.1355485598321</v>
+        <v>444.0698297189007</v>
       </c>
       <c r="O20" t="n">
-        <v>622.8542841136414</v>
+        <v>591.78856527271</v>
       </c>
       <c r="P20" t="n">
-        <v>808</v>
+        <v>776.9342811590686</v>
       </c>
       <c r="Q20" t="n">
-        <v>808</v>
+        <v>808.0000000000002</v>
       </c>
       <c r="R20" t="n">
-        <v>808</v>
+        <v>808.0000000000002</v>
       </c>
       <c r="S20" t="n">
-        <v>808</v>
+        <v>808.0000000000002</v>
       </c>
       <c r="T20" t="n">
-        <v>603.9595959595939</v>
+        <v>808.0000000000002</v>
       </c>
       <c r="U20" t="n">
-        <v>603.9595959595939</v>
+        <v>808.0000000000002</v>
       </c>
       <c r="V20" t="n">
-        <v>603.9595959595939</v>
+        <v>603.9595959595948</v>
       </c>
       <c r="W20" t="n">
-        <v>603.9595959595939</v>
+        <v>603.9595959595948</v>
       </c>
       <c r="X20" t="n">
-        <v>603.9595959595939</v>
+        <v>403.0279928844196</v>
       </c>
       <c r="Y20" t="n">
-        <v>516.3182000267627</v>
+        <v>198.9875888440147</v>
       </c>
     </row>
     <row r="21">
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.3718147122571</v>
+        <v>16.16</v>
       </c>
       <c r="C21" t="n">
-        <v>105.6648324440558</v>
+        <v>16.16</v>
       </c>
       <c r="D21" t="n">
-        <v>58.25302749688144</v>
+        <v>16.16</v>
       </c>
       <c r="E21" t="n">
         <v>16.16</v>
@@ -5819,55 +5819,55 @@
         <v>16.16</v>
       </c>
       <c r="I21" t="n">
+        <v>105.3989681203763</v>
+      </c>
+      <c r="J21" t="n">
+        <v>305.3789681203763</v>
+      </c>
+      <c r="K21" t="n">
+        <v>313.0599770811311</v>
+      </c>
+      <c r="L21" t="n">
+        <v>513.0399770811312</v>
+      </c>
+      <c r="M21" t="n">
+        <v>604.946846598184</v>
+      </c>
+      <c r="N21" t="n">
+        <v>735.1037010042288</v>
+      </c>
+      <c r="O21" t="n">
+        <v>759.4446409316569</v>
+      </c>
+      <c r="P21" t="n">
+        <v>786.7624116224158</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>808.0000000000002</v>
+      </c>
+      <c r="R21" t="n">
+        <v>808.0000000000002</v>
+      </c>
+      <c r="S21" t="n">
+        <v>653.8391080974959</v>
+      </c>
+      <c r="T21" t="n">
+        <v>551.2646168352845</v>
+      </c>
+      <c r="U21" t="n">
+        <v>451.098444407423</v>
+      </c>
+      <c r="V21" t="n">
+        <v>336.4412048200289</v>
+      </c>
+      <c r="W21" t="n">
+        <v>203.7410604666667</v>
+      </c>
+      <c r="X21" t="n">
+        <v>83.67768728950759</v>
+      </c>
+      <c r="Y21" t="n">
         <v>16.16</v>
-      </c>
-      <c r="J21" t="n">
-        <v>45.27547950796338</v>
-      </c>
-      <c r="K21" t="n">
-        <v>52.95648846871813</v>
-      </c>
-      <c r="L21" t="n">
-        <v>252.9364884687182</v>
-      </c>
-      <c r="M21" t="n">
-        <v>252.9364884687182</v>
-      </c>
-      <c r="N21" t="n">
-        <v>383.0933428747629</v>
-      </c>
-      <c r="O21" t="n">
-        <v>583.0733428747629</v>
-      </c>
-      <c r="P21" t="n">
-        <v>610.3911135655219</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>808</v>
-      </c>
-      <c r="R21" t="n">
-        <v>808</v>
-      </c>
-      <c r="S21" t="n">
-        <v>808</v>
-      </c>
-      <c r="T21" t="n">
-        <v>705.4255087377886</v>
-      </c>
-      <c r="U21" t="n">
-        <v>605.259336309927</v>
-      </c>
-      <c r="V21" t="n">
-        <v>490.6020967225329</v>
-      </c>
-      <c r="W21" t="n">
-        <v>357.9019523691708</v>
-      </c>
-      <c r="X21" t="n">
-        <v>350.1576221995914</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>250.7723769812739</v>
       </c>
     </row>
     <row r="22">
@@ -5877,49 +5877,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>308.8024558766118</v>
+        <v>411.3181990984179</v>
       </c>
       <c r="C22" t="n">
-        <v>336.7944616950475</v>
+        <v>435.7646582366399</v>
       </c>
       <c r="D22" t="n">
-        <v>336.7944616950475</v>
+        <v>451.07380236164</v>
       </c>
       <c r="E22" t="n">
-        <v>356.6133659064606</v>
+        <v>451.07380236164</v>
       </c>
       <c r="F22" t="n">
-        <v>382.964338498396</v>
+        <v>477.4247749535755</v>
       </c>
       <c r="G22" t="n">
-        <v>438.9393240574125</v>
+        <v>533.3997605125919</v>
       </c>
       <c r="H22" t="n">
-        <v>438.9393240574125</v>
+        <v>610.049022393301</v>
       </c>
       <c r="I22" t="n">
-        <v>557.3340185469154</v>
+        <v>728.443716882804</v>
       </c>
       <c r="J22" t="n">
-        <v>728.4437168828038</v>
+        <v>728.443716882804</v>
       </c>
       <c r="K22" t="n">
-        <v>808</v>
+        <v>808.0000000000002</v>
       </c>
       <c r="L22" t="n">
-        <v>808</v>
+        <v>771.955798681495</v>
       </c>
       <c r="M22" t="n">
-        <v>808</v>
+        <v>771.955798681495</v>
       </c>
       <c r="N22" t="n">
-        <v>808</v>
+        <v>771.955798681495</v>
       </c>
       <c r="O22" t="n">
-        <v>679.9896781234369</v>
+        <v>679.9896781234343</v>
       </c>
       <c r="P22" t="n">
-        <v>475.9492740830312</v>
+        <v>475.9492740830301</v>
       </c>
       <c r="Q22" t="n">
         <v>271.908870042626</v>
@@ -5934,19 +5934,19 @@
         <v>108.6971086670016</v>
       </c>
       <c r="U22" t="n">
-        <v>108.6971086670016</v>
+        <v>257.2698514692227</v>
       </c>
       <c r="V22" t="n">
-        <v>209.5085015529475</v>
+        <v>257.2698514692227</v>
       </c>
       <c r="W22" t="n">
-        <v>228.6350265070938</v>
+        <v>331.1507697289001</v>
       </c>
       <c r="X22" t="n">
-        <v>281.6558175312874</v>
+        <v>384.1715607530936</v>
       </c>
       <c r="Y22" t="n">
-        <v>295.0551182103196</v>
+        <v>397.5708614321258</v>
       </c>
     </row>
     <row r="23">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>214.0152834622421</v>
+        <v>16.48</v>
       </c>
       <c r="C23" t="n">
-        <v>214.0152834622421</v>
+        <v>16.48</v>
       </c>
       <c r="D23" t="n">
-        <v>214.0152834622421</v>
+        <v>16.48</v>
       </c>
       <c r="E23" t="n">
-        <v>214.0152834622421</v>
+        <v>16.48</v>
       </c>
       <c r="F23" t="n">
-        <v>110.0863655753614</v>
+        <v>16.48</v>
       </c>
       <c r="G23" t="n">
-        <v>110.0863655753614</v>
+        <v>16.48</v>
       </c>
       <c r="H23" t="n">
         <v>16.48</v>
@@ -5983,22 +5983,22 @@
         <v>91.23105818921989</v>
       </c>
       <c r="K23" t="n">
-        <v>287.6447598161137</v>
+        <v>255.2586957771596</v>
       </c>
       <c r="L23" t="n">
-        <v>491.1355485598323</v>
+        <v>458.7494845208782</v>
       </c>
       <c r="M23" t="n">
-        <v>491.1355485598323</v>
+        <v>458.7494845208782</v>
       </c>
       <c r="N23" t="n">
-        <v>491.1355485598323</v>
+        <v>458.7494845208782</v>
       </c>
       <c r="O23" t="n">
-        <v>638.8542841136416</v>
+        <v>606.4682200746875</v>
       </c>
       <c r="P23" t="n">
-        <v>824.0000000000002</v>
+        <v>791.6139359610461</v>
       </c>
       <c r="Q23" t="n">
         <v>824.0000000000002</v>
@@ -6010,22 +6010,22 @@
         <v>824.0000000000002</v>
       </c>
       <c r="T23" t="n">
-        <v>615.9191919191901</v>
+        <v>824.0000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>603.9135793769647</v>
+        <v>615.9191919191907</v>
       </c>
       <c r="V23" t="n">
-        <v>603.9135793769647</v>
+        <v>407.8383838383817</v>
       </c>
       <c r="W23" t="n">
-        <v>395.8327712961558</v>
+        <v>224.5608080808086</v>
       </c>
       <c r="X23" t="n">
-        <v>395.8327712961558</v>
+        <v>16.48</v>
       </c>
       <c r="Y23" t="n">
-        <v>395.8327712961558</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>186.9368957371561</v>
+        <v>225.3521056363622</v>
       </c>
       <c r="C24" t="n">
-        <v>127.2400144790558</v>
+        <v>165.6552243782619</v>
       </c>
       <c r="D24" t="n">
-        <v>80.83831054198244</v>
+        <v>119.2535204411886</v>
       </c>
       <c r="E24" t="n">
-        <v>39.75538405520201</v>
+        <v>78.17059395440812</v>
       </c>
       <c r="F24" t="n">
-        <v>39.75538405520201</v>
+        <v>40.15418755251229</v>
       </c>
       <c r="G24" t="n">
-        <v>16.48</v>
+        <v>40.15418755251229</v>
       </c>
       <c r="H24" t="n">
         <v>16.48</v>
       </c>
       <c r="I24" t="n">
-        <v>16.48</v>
+        <v>106.7089681203763</v>
       </c>
       <c r="J24" t="n">
-        <v>220.42</v>
+        <v>128.4494241410341</v>
       </c>
       <c r="K24" t="n">
-        <v>424.3600000000001</v>
+        <v>136.1304331017889</v>
       </c>
       <c r="L24" t="n">
-        <v>461.3060166132077</v>
+        <v>173.0764497149965</v>
       </c>
       <c r="M24" t="n">
-        <v>461.3060166132077</v>
+        <v>265.9733192320493</v>
       </c>
       <c r="N24" t="n">
-        <v>461.3060166132077</v>
+        <v>397.1201736380941</v>
       </c>
       <c r="O24" t="n">
-        <v>665.2460166132078</v>
+        <v>421.4611135655221</v>
       </c>
       <c r="P24" t="n">
-        <v>824.0000000000002</v>
+        <v>625.4011135655221</v>
       </c>
       <c r="Q24" t="n">
         <v>824.0000000000002</v>
       </c>
       <c r="R24" t="n">
-        <v>619.9550360873625</v>
+        <v>824.0000000000002</v>
       </c>
       <c r="S24" t="n">
-        <v>619.9550360873625</v>
+        <v>824.0000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>619.9550360873625</v>
+        <v>722.4356097478899</v>
       </c>
       <c r="U24" t="n">
-        <v>520.7989646696019</v>
+        <v>623.2795383301293</v>
       </c>
       <c r="V24" t="n">
-        <v>407.1518260923088</v>
+        <v>526.1709832705526</v>
       </c>
       <c r="W24" t="n">
-        <v>389.38062916313</v>
+        <v>526.1709832705526</v>
       </c>
       <c r="X24" t="n">
-        <v>270.3273569960719</v>
+        <v>407.1177111034945</v>
       </c>
       <c r="Y24" t="n">
-        <v>270.3273569960719</v>
+        <v>308.742566895278</v>
       </c>
     </row>
     <row r="25">
@@ -6114,28 +6114,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>444.5086737246866</v>
+        <v>253.2781186299048</v>
       </c>
       <c r="C25" t="n">
-        <v>444.5086737246866</v>
+        <v>253.2781186299048</v>
       </c>
       <c r="D25" t="n">
-        <v>460.8078178496866</v>
+        <v>269.2151998143387</v>
       </c>
       <c r="E25" t="n">
-        <v>481.6167220610997</v>
+        <v>290.0241040257517</v>
       </c>
       <c r="F25" t="n">
-        <v>508.9576946530352</v>
+        <v>317.3650766176872</v>
       </c>
       <c r="G25" t="n">
-        <v>565.9226802120515</v>
+        <v>374.3300621767037</v>
       </c>
       <c r="H25" t="n">
-        <v>643.5619420927605</v>
+        <v>451.9693240574127</v>
       </c>
       <c r="I25" t="n">
-        <v>743.453716882804</v>
+        <v>571.3540185469157</v>
       </c>
       <c r="J25" t="n">
         <v>743.453716882804</v>
@@ -6159,10 +6159,10 @@
         <v>279.5092516053065</v>
       </c>
       <c r="Q25" t="n">
-        <v>275.2591730729291</v>
+        <v>224.5608080808081</v>
       </c>
       <c r="R25" t="n">
-        <v>67.17836499212092</v>
+        <v>16.48</v>
       </c>
       <c r="S25" t="n">
         <v>16.48</v>
@@ -6171,19 +6171,19 @@
         <v>110.0071086670016</v>
       </c>
       <c r="U25" t="n">
-        <v>259.5698514692227</v>
+        <v>110.0071086670016</v>
       </c>
       <c r="V25" t="n">
-        <v>361.3712443551686</v>
+        <v>110.0071086670016</v>
       </c>
       <c r="W25" t="n">
-        <v>361.3712443551686</v>
+        <v>184.878026926679</v>
       </c>
       <c r="X25" t="n">
-        <v>415.3820353793622</v>
+        <v>238.8888179508725</v>
       </c>
       <c r="Y25" t="n">
-        <v>429.7713360583944</v>
+        <v>253.2781186299048</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>331.8287773806769</v>
+        <v>496.3232323232323</v>
       </c>
       <c r="C26" t="n">
-        <v>164.1520097039077</v>
+        <v>496.3232323232323</v>
       </c>
       <c r="D26" t="n">
-        <v>164.1520097039077</v>
+        <v>339.4149942021719</v>
       </c>
       <c r="E26" t="n">
-        <v>13.28</v>
+        <v>339.4149942021719</v>
       </c>
       <c r="F26" t="n">
-        <v>13.28</v>
+        <v>303.3054158018283</v>
       </c>
       <c r="G26" t="n">
-        <v>13.28</v>
+        <v>154.3611130501089</v>
       </c>
       <c r="H26" t="n">
         <v>13.28</v>
@@ -6226,7 +6226,7 @@
         <v>416.3986957771596</v>
       </c>
       <c r="M26" t="n">
-        <v>355.2347375982796</v>
+        <v>351.9412644461907</v>
       </c>
       <c r="N26" t="n">
         <v>351.9412644461907</v>
@@ -6250,19 +6250,19 @@
         <v>664</v>
       </c>
       <c r="U26" t="n">
-        <v>664</v>
+        <v>496.3232323232323</v>
       </c>
       <c r="V26" t="n">
-        <v>664</v>
+        <v>496.3232323232323</v>
       </c>
       <c r="W26" t="n">
-        <v>664</v>
+        <v>496.3232323232323</v>
       </c>
       <c r="X26" t="n">
-        <v>499.5055450574458</v>
+        <v>496.3232323232323</v>
       </c>
       <c r="Y26" t="n">
-        <v>499.5055450574458</v>
+        <v>496.3232323232323</v>
       </c>
     </row>
     <row r="27">
@@ -6293,52 +6293,52 @@
         <v>13.28</v>
       </c>
       <c r="I27" t="n">
-        <v>13.28</v>
+        <v>56.97896812037627</v>
       </c>
       <c r="J27" t="n">
-        <v>13.28</v>
+        <v>221.3189681203763</v>
       </c>
       <c r="K27" t="n">
-        <v>134.0339833867924</v>
+        <v>338.7095319280826</v>
       </c>
       <c r="L27" t="n">
-        <v>170.9799999999999</v>
+        <v>375.6555485412902</v>
       </c>
       <c r="M27" t="n">
-        <v>170.9799999999999</v>
+        <v>375.6555485412902</v>
       </c>
       <c r="N27" t="n">
-        <v>170.9799999999999</v>
+        <v>460.2724029473349</v>
       </c>
       <c r="O27" t="n">
-        <v>335.3199999999999</v>
+        <v>484.6133428747629</v>
       </c>
       <c r="P27" t="n">
-        <v>499.66</v>
+        <v>511.9311135655219</v>
       </c>
       <c r="Q27" t="n">
         <v>664</v>
       </c>
       <c r="R27" t="n">
-        <v>655.2374922631229</v>
+        <v>496.3232323232304</v>
       </c>
       <c r="S27" t="n">
-        <v>655.2374922631229</v>
+        <v>328.6464646464611</v>
       </c>
       <c r="T27" t="n">
-        <v>655.2374922631229</v>
+        <v>328.6464646464611</v>
       </c>
       <c r="U27" t="n">
-        <v>508.6066733706149</v>
+        <v>328.6464646464611</v>
       </c>
       <c r="V27" t="n">
-        <v>347.4847873185743</v>
+        <v>326.8066593597325</v>
       </c>
       <c r="W27" t="n">
-        <v>179.8080196418056</v>
+        <v>159.129891682964</v>
       </c>
       <c r="X27" t="n">
-        <v>13.28</v>
+        <v>159.129891682964</v>
       </c>
       <c r="Y27" t="n">
         <v>13.28</v>
@@ -6351,55 +6351,55 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>221.9647714803743</v>
+        <v>189.1714857738466</v>
       </c>
       <c r="C28" t="n">
-        <v>204.0604819368948</v>
+        <v>171.2671962303671</v>
       </c>
       <c r="D28" t="n">
-        <v>204.0604819368948</v>
+        <v>140.4225315277858</v>
       </c>
       <c r="E28" t="n">
-        <v>204.0604819368948</v>
+        <v>114.1791933086378</v>
       </c>
       <c r="F28" t="n">
-        <v>184.4818395452363</v>
+        <v>94.60055091697927</v>
       </c>
       <c r="G28" t="n">
-        <v>194.9168251042527</v>
+        <v>105.0355364759957</v>
       </c>
       <c r="H28" t="n">
-        <v>226.0260869849617</v>
+        <v>136.1447983567047</v>
       </c>
       <c r="I28" t="n">
-        <v>321.003622970225</v>
+        <v>231.122334341968</v>
       </c>
       <c r="J28" t="n">
-        <v>485.3436229702249</v>
+        <v>395.462334341968</v>
       </c>
       <c r="K28" t="n">
-        <v>519.3599060874212</v>
+        <v>429.4786174591642</v>
       </c>
       <c r="L28" t="n">
-        <v>436.8510583042695</v>
+        <v>346.9697696760126</v>
       </c>
       <c r="M28" t="n">
-        <v>269.1742906275002</v>
+        <v>179.2930019992449</v>
       </c>
       <c r="N28" t="n">
-        <v>180.9567676767696</v>
+        <v>111.4531124668684</v>
       </c>
       <c r="O28" t="n">
-        <v>180.9567676767696</v>
+        <v>111.4531124668684</v>
       </c>
       <c r="P28" t="n">
-        <v>13.28</v>
+        <v>111.4531124668684</v>
       </c>
       <c r="Q28" t="n">
-        <v>13.28</v>
+        <v>111.4531124668684</v>
       </c>
       <c r="R28" t="n">
-        <v>13.28</v>
+        <v>111.4531124668684</v>
       </c>
       <c r="S28" t="n">
         <v>13.28</v>
@@ -6420,7 +6420,7 @@
         <v>254.4029536390396</v>
       </c>
       <c r="Y28" t="n">
-        <v>254.4029536390396</v>
+        <v>221.6096679325119</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>339.81393303742</v>
+        <v>424.7685501115792</v>
       </c>
       <c r="C29" t="n">
-        <v>201.9608237010626</v>
+        <v>286.9154407752217</v>
       </c>
       <c r="D29" t="n">
-        <v>103.6384441658607</v>
+        <v>188.5930612400199</v>
       </c>
       <c r="E29" t="n">
-        <v>103.6384441658607</v>
+        <v>188.5930612400199</v>
       </c>
       <c r="F29" t="n">
-        <v>103.6384441658607</v>
+        <v>95.77525446425034</v>
       </c>
       <c r="G29" t="n">
-        <v>13.28</v>
+        <v>95.77525446425034</v>
       </c>
       <c r="H29" t="n">
         <v>13.28</v>
@@ -6487,19 +6487,19 @@
         <v>664</v>
       </c>
       <c r="U29" t="n">
-        <v>507.4907007141877</v>
+        <v>664</v>
       </c>
       <c r="V29" t="n">
-        <v>507.4907007141877</v>
+        <v>664</v>
       </c>
       <c r="W29" t="n">
-        <v>507.4907007141877</v>
+        <v>664</v>
       </c>
       <c r="X29" t="n">
-        <v>507.4907007141877</v>
+        <v>664</v>
       </c>
       <c r="Y29" t="n">
-        <v>507.4907007141877</v>
+        <v>592.4453177883469</v>
       </c>
     </row>
     <row r="30">
@@ -6509,13 +6509,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>143.4702301989353</v>
+        <v>148.7890076492282</v>
       </c>
       <c r="C30" t="n">
-        <v>94.88446005194611</v>
+        <v>100.203237502239</v>
       </c>
       <c r="D30" t="n">
-        <v>94.88446005194611</v>
+        <v>64.91264467627678</v>
       </c>
       <c r="E30" t="n">
         <v>64.91264467627678</v>
@@ -6530,55 +6530,55 @@
         <v>13.28</v>
       </c>
       <c r="I30" t="n">
-        <v>13.28</v>
+        <v>114.3989681203763</v>
       </c>
       <c r="J30" t="n">
-        <v>138.9580511118172</v>
+        <v>278.7389681203763</v>
       </c>
       <c r="K30" t="n">
-        <v>146.6390600725719</v>
+        <v>286.419977081131</v>
       </c>
       <c r="L30" t="n">
-        <v>310.9790600725719</v>
+        <v>323.3659936943386</v>
       </c>
       <c r="M30" t="n">
-        <v>310.9790600725719</v>
+        <v>323.3659936943386</v>
       </c>
       <c r="N30" t="n">
-        <v>310.9790600725719</v>
+        <v>465.4028481003834</v>
       </c>
       <c r="O30" t="n">
-        <v>335.3199999999999</v>
+        <v>489.7437880278114</v>
       </c>
       <c r="P30" t="n">
-        <v>499.66</v>
+        <v>517.0615587185704</v>
       </c>
       <c r="Q30" t="n">
         <v>664</v>
       </c>
       <c r="R30" t="n">
-        <v>664</v>
+        <v>537.765435619006</v>
       </c>
       <c r="S30" t="n">
-        <v>617.3627794927206</v>
+        <v>537.765435619006</v>
       </c>
       <c r="T30" t="n">
-        <v>526.9095003517214</v>
+        <v>447.3121564780067</v>
       </c>
       <c r="U30" t="n">
-        <v>438.8645400450719</v>
+        <v>359.2671961713572</v>
       </c>
       <c r="V30" t="n">
-        <v>336.32851257889</v>
+        <v>256.7311687051753</v>
       </c>
       <c r="W30" t="n">
-        <v>215.7495803467399</v>
+        <v>256.7311687051753</v>
       </c>
       <c r="X30" t="n">
-        <v>215.7495803467399</v>
+        <v>148.7890076492282</v>
       </c>
       <c r="Y30" t="n">
-        <v>215.7495803467399</v>
+        <v>148.7890076492282</v>
       </c>
     </row>
     <row r="31">
@@ -6588,28 +6588,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>350.0217897523849</v>
+        <v>240.3500313239872</v>
       </c>
       <c r="C31" t="n">
-        <v>350.0217897523849</v>
+        <v>280.2220371424229</v>
       </c>
       <c r="D31" t="n">
-        <v>350.0217897523849</v>
+        <v>307.411181267423</v>
       </c>
       <c r="E31" t="n">
-        <v>350.0217897523849</v>
+        <v>339.1100854788361</v>
       </c>
       <c r="F31" t="n">
-        <v>350.0217897523849</v>
+        <v>377.3410580707716</v>
       </c>
       <c r="G31" t="n">
-        <v>350.0217897523849</v>
+        <v>445.196043629788</v>
       </c>
       <c r="H31" t="n">
-        <v>438.5510516330939</v>
+        <v>533.725305510497</v>
       </c>
       <c r="I31" t="n">
-        <v>590.9485876183579</v>
+        <v>664</v>
       </c>
       <c r="J31" t="n">
         <v>664</v>
@@ -6618,22 +6618,22 @@
         <v>664</v>
       </c>
       <c r="L31" t="n">
-        <v>640.0770108027069</v>
+        <v>664</v>
       </c>
       <c r="M31" t="n">
-        <v>522.8589896807406</v>
+        <v>546.7819788780337</v>
       </c>
       <c r="N31" t="n">
-        <v>355.1822220039729</v>
+        <v>379.105211201266</v>
       </c>
       <c r="O31" t="n">
-        <v>187.5054543272052</v>
+        <v>211.4284435244983</v>
       </c>
       <c r="P31" t="n">
-        <v>180.9567676767677</v>
+        <v>43.75167584773061</v>
       </c>
       <c r="Q31" t="n">
-        <v>180.9567676767677</v>
+        <v>13.28</v>
       </c>
       <c r="R31" t="n">
         <v>13.28</v>
@@ -6642,22 +6642,22 @@
         <v>13.28</v>
       </c>
       <c r="T31" t="n">
-        <v>13.28</v>
+        <v>117.6971086670023</v>
       </c>
       <c r="U31" t="n">
-        <v>173.7327428022218</v>
+        <v>189.4433929786628</v>
       </c>
       <c r="V31" t="n">
-        <v>173.7327428022218</v>
+        <v>189.4433929786628</v>
       </c>
       <c r="W31" t="n">
-        <v>259.4936610618992</v>
+        <v>189.4433929786628</v>
       </c>
       <c r="X31" t="n">
-        <v>324.3944520860928</v>
+        <v>189.4433929786628</v>
       </c>
       <c r="Y31" t="n">
-        <v>324.3944520860928</v>
+        <v>214.722693657695</v>
       </c>
     </row>
     <row r="32">
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>93.44493899683702</v>
+        <v>330.7167434084224</v>
       </c>
       <c r="C32" t="n">
-        <v>93.44493899683702</v>
+        <v>330.7167434084224</v>
       </c>
       <c r="D32" t="n">
-        <v>93.44493899683702</v>
+        <v>244.5155759944327</v>
       </c>
       <c r="E32" t="n">
-        <v>13.28</v>
+        <v>164.3506369975956</v>
       </c>
       <c r="F32" t="n">
-        <v>13.28</v>
+        <v>83.65404234303821</v>
       </c>
       <c r="G32" t="n">
-        <v>13.28</v>
+        <v>83.65404234303821</v>
       </c>
       <c r="H32" t="n">
         <v>13.28</v>
@@ -6724,19 +6724,19 @@
         <v>664</v>
       </c>
       <c r="U32" t="n">
-        <v>496.323232323231</v>
+        <v>496.3232323232312</v>
       </c>
       <c r="V32" t="n">
-        <v>428.7984743503739</v>
+        <v>330.7167434084224</v>
       </c>
       <c r="W32" t="n">
-        <v>261.1217066736055</v>
+        <v>330.7167434084224</v>
       </c>
       <c r="X32" t="n">
-        <v>261.1217066736055</v>
+        <v>330.7167434084224</v>
       </c>
       <c r="Y32" t="n">
-        <v>93.44493899683702</v>
+        <v>330.7167434084224</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>13.76492514306783</v>
+        <v>106.0335502976248</v>
       </c>
       <c r="C33" t="n">
-        <v>13.76492514306783</v>
+        <v>69.56899227184778</v>
       </c>
       <c r="D33" t="n">
-        <v>13.76492514306783</v>
+        <v>46.39961156709764</v>
       </c>
       <c r="E33" t="n">
-        <v>13.76492514306783</v>
+        <v>28.54900831264044</v>
       </c>
       <c r="F33" t="n">
-        <v>13.76492514306783</v>
+        <v>13.76492514306785</v>
       </c>
       <c r="G33" t="n">
-        <v>13.72186432018906</v>
+        <v>13.72186432018907</v>
       </c>
       <c r="H33" t="n">
         <v>13.28</v>
@@ -6770,19 +6770,19 @@
         <v>13.28</v>
       </c>
       <c r="J33" t="n">
-        <v>150.5240529425186</v>
+        <v>177.62</v>
       </c>
       <c r="K33" t="n">
-        <v>158.2050619032734</v>
+        <v>185.3010089607548</v>
       </c>
       <c r="L33" t="n">
-        <v>195.1510785164809</v>
+        <v>222.2470255739623</v>
       </c>
       <c r="M33" t="n">
-        <v>310.8179480335338</v>
+        <v>294.0844349757683</v>
       </c>
       <c r="N33" t="n">
-        <v>310.8179480335338</v>
+        <v>448.001289381813</v>
       </c>
       <c r="O33" t="n">
         <v>472.342229309241</v>
@@ -6794,28 +6794,28 @@
         <v>664</v>
       </c>
       <c r="R33" t="n">
-        <v>496.3232323232315</v>
+        <v>664</v>
       </c>
       <c r="S33" t="n">
-        <v>496.3232323232315</v>
+        <v>664</v>
       </c>
       <c r="T33" t="n">
-        <v>417.9911653034443</v>
+        <v>585.6679329802129</v>
       </c>
       <c r="U33" t="n">
-        <v>342.067417118007</v>
+        <v>509.7441847947755</v>
       </c>
       <c r="V33" t="n">
-        <v>251.6526017730371</v>
+        <v>419.3293694498057</v>
       </c>
       <c r="W33" t="n">
-        <v>149.0658841455536</v>
+        <v>337.1554582348456</v>
       </c>
       <c r="X33" t="n">
-        <v>149.0658841455536</v>
+        <v>241.3345093001107</v>
       </c>
       <c r="Y33" t="n">
-        <v>73.92306316966037</v>
+        <v>166.1916883242174</v>
       </c>
     </row>
     <row r="34">
@@ -6825,28 +6825,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>312.2731021698169</v>
+        <v>206.3578996911951</v>
       </c>
       <c r="C34" t="n">
-        <v>343.2242180699688</v>
+        <v>206.3578996911951</v>
       </c>
       <c r="D34" t="n">
-        <v>343.2242180699688</v>
+        <v>245.4270438161952</v>
       </c>
       <c r="E34" t="n">
-        <v>343.2242180699688</v>
+        <v>289.0059480276082</v>
       </c>
       <c r="F34" t="n">
-        <v>393.3351906619043</v>
+        <v>289.0059480276082</v>
       </c>
       <c r="G34" t="n">
-        <v>393.3351906619043</v>
+        <v>289.0059480276082</v>
       </c>
       <c r="H34" t="n">
-        <v>493.7444525426133</v>
+        <v>389.4152099083173</v>
       </c>
       <c r="I34" t="n">
-        <v>658.0219885278766</v>
+        <v>531.5699043978202</v>
       </c>
       <c r="J34" t="n">
         <v>664</v>
@@ -6855,46 +6855,46 @@
         <v>664</v>
       </c>
       <c r="L34" t="n">
-        <v>664</v>
+        <v>652.198222923919</v>
       </c>
       <c r="M34" t="n">
-        <v>664</v>
+        <v>652.198222923919</v>
       </c>
       <c r="N34" t="n">
-        <v>516.310303030306</v>
+        <v>493.8376070674399</v>
       </c>
       <c r="O34" t="n">
-        <v>516.310303030306</v>
+        <v>493.8376070674399</v>
       </c>
       <c r="P34" t="n">
-        <v>348.6335353535372</v>
+        <v>376.0995771133341</v>
       </c>
       <c r="Q34" t="n">
-        <v>180.9567676767685</v>
+        <v>208.4228094365654</v>
       </c>
       <c r="R34" t="n">
-        <v>13.28</v>
+        <v>40.74604175979767</v>
       </c>
       <c r="S34" t="n">
         <v>13.28</v>
       </c>
       <c r="T34" t="n">
-        <v>13.28</v>
+        <v>129.5771086670016</v>
       </c>
       <c r="U34" t="n">
-        <v>13.28</v>
+        <v>129.5771086670016</v>
       </c>
       <c r="V34" t="n">
-        <v>137.851392885946</v>
+        <v>129.5771086670016</v>
       </c>
       <c r="W34" t="n">
-        <v>235.4923111456234</v>
+        <v>129.5771086670016</v>
       </c>
       <c r="X34" t="n">
-        <v>312.2731021698169</v>
+        <v>206.3578996911951</v>
       </c>
       <c r="Y34" t="n">
-        <v>312.2731021698169</v>
+        <v>206.3578996911951</v>
       </c>
     </row>
     <row r="35">
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>171.6821710414857</v>
+        <v>161.8912743876868</v>
       </c>
       <c r="C35" t="n">
-        <v>171.6821710414857</v>
+        <v>161.8912743876868</v>
       </c>
       <c r="D35" t="n">
-        <v>171.6821710414857</v>
+        <v>161.8912743876868</v>
       </c>
       <c r="E35" t="n">
-        <v>91.51723204464865</v>
+        <v>161.8912743876868</v>
       </c>
       <c r="F35" t="n">
-        <v>91.51723204464865</v>
+        <v>161.8912743876868</v>
       </c>
       <c r="G35" t="n">
-        <v>13.28</v>
+        <v>83.65404234303821</v>
       </c>
       <c r="H35" t="n">
         <v>13.28</v>
@@ -6955,25 +6955,25 @@
         <v>664</v>
       </c>
       <c r="S35" t="n">
-        <v>522.4170072957603</v>
+        <v>664</v>
       </c>
       <c r="T35" t="n">
-        <v>354.7402396189914</v>
+        <v>664</v>
       </c>
       <c r="U35" t="n">
-        <v>187.0634719422224</v>
+        <v>664</v>
       </c>
       <c r="V35" t="n">
-        <v>187.0634719422224</v>
+        <v>496.323232323232</v>
       </c>
       <c r="W35" t="n">
-        <v>171.6821710414857</v>
+        <v>328.6464646464641</v>
       </c>
       <c r="X35" t="n">
-        <v>171.6821710414857</v>
+        <v>161.8912743876868</v>
       </c>
       <c r="Y35" t="n">
-        <v>171.6821710414857</v>
+        <v>161.8912743876868</v>
       </c>
     </row>
     <row r="36">
@@ -6983,13 +6983,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>88.18294704316764</v>
+        <v>82.8641695928747</v>
       </c>
       <c r="C36" t="n">
-        <v>51.71838901739058</v>
+        <v>46.39961156709764</v>
       </c>
       <c r="D36" t="n">
-        <v>28.54900831264044</v>
+        <v>46.39961156709764</v>
       </c>
       <c r="E36" t="n">
         <v>28.54900831264044</v>
@@ -7004,25 +7004,25 @@
         <v>13.28</v>
       </c>
       <c r="I36" t="n">
-        <v>13.28</v>
+        <v>126.2789681203763</v>
       </c>
       <c r="J36" t="n">
-        <v>13.28</v>
+        <v>290.6189681203763</v>
       </c>
       <c r="K36" t="n">
-        <v>20.96100896075475</v>
+        <v>298.299977081131</v>
       </c>
       <c r="L36" t="n">
-        <v>57.90702557396233</v>
+        <v>335.2459936943386</v>
       </c>
       <c r="M36" t="n">
-        <v>57.90702557396233</v>
+        <v>335.2459936943386</v>
       </c>
       <c r="N36" t="n">
-        <v>211.8238799800071</v>
+        <v>335.2459936943386</v>
       </c>
       <c r="O36" t="n">
-        <v>335.3199999999999</v>
+        <v>359.5869336217666</v>
       </c>
       <c r="P36" t="n">
         <v>499.66</v>
@@ -7034,25 +7034,25 @@
         <v>664</v>
       </c>
       <c r="S36" t="n">
-        <v>534.0815323399199</v>
+        <v>664</v>
       </c>
       <c r="T36" t="n">
-        <v>455.7494653201327</v>
+        <v>585.6679329802129</v>
       </c>
       <c r="U36" t="n">
-        <v>455.7494653201327</v>
+        <v>509.7441847947755</v>
       </c>
       <c r="V36" t="n">
-        <v>365.3346499751628</v>
+        <v>419.3293694498057</v>
       </c>
       <c r="W36" t="n">
-        <v>256.876929864225</v>
+        <v>313.9860775300955</v>
       </c>
       <c r="X36" t="n">
-        <v>223.4839060456535</v>
+        <v>218.1651285953606</v>
       </c>
       <c r="Y36" t="n">
-        <v>148.3410850697602</v>
+        <v>143.0223076194673</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>235.4139876941992</v>
+        <v>301.8846652720034</v>
       </c>
       <c r="C37" t="n">
-        <v>287.1659935126349</v>
+        <v>351.0967316319259</v>
       </c>
       <c r="D37" t="n">
-        <v>326.235137637635</v>
+        <v>390.165875756926</v>
       </c>
       <c r="E37" t="n">
-        <v>369.8140418490481</v>
+        <v>433.744779968339</v>
       </c>
       <c r="F37" t="n">
-        <v>419.9250144409835</v>
+        <v>483.8557525602745</v>
       </c>
       <c r="G37" t="n">
-        <v>499.66</v>
+        <v>563.5907381192909</v>
       </c>
       <c r="H37" t="n">
-        <v>499.66</v>
+        <v>664</v>
       </c>
       <c r="I37" t="n">
-        <v>499.66</v>
+        <v>664</v>
       </c>
       <c r="J37" t="n">
         <v>664</v>
@@ -7098,40 +7098,40 @@
         <v>652.198222923919</v>
       </c>
       <c r="N37" t="n">
-        <v>543.776344790104</v>
+        <v>652.198222923919</v>
       </c>
       <c r="O37" t="n">
-        <v>376.0995771133353</v>
+        <v>516.3103030303051</v>
       </c>
       <c r="P37" t="n">
-        <v>376.0995771133353</v>
+        <v>348.6335353535364</v>
       </c>
       <c r="Q37" t="n">
-        <v>208.4228094365662</v>
+        <v>180.9567676767677</v>
       </c>
       <c r="R37" t="n">
-        <v>40.74604175979767</v>
+        <v>13.28</v>
       </c>
       <c r="S37" t="n">
         <v>13.28</v>
       </c>
       <c r="T37" t="n">
-        <v>13.28</v>
+        <v>129.5771086670016</v>
       </c>
       <c r="U37" t="n">
-        <v>13.28</v>
+        <v>129.5771086670016</v>
       </c>
       <c r="V37" t="n">
-        <v>137.851392885946</v>
+        <v>129.5771086670016</v>
       </c>
       <c r="W37" t="n">
-        <v>198.2546870151669</v>
+        <v>227.218026926679</v>
       </c>
       <c r="X37" t="n">
-        <v>198.2546870151669</v>
+        <v>227.218026926679</v>
       </c>
       <c r="Y37" t="n">
-        <v>235.4139876941992</v>
+        <v>264.3773276057112</v>
       </c>
     </row>
     <row r="38">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>219.269331279996</v>
+        <v>453.5352103047317</v>
       </c>
       <c r="C38" t="n">
-        <v>92.52733305474966</v>
+        <v>326.7932120794853</v>
       </c>
       <c r="D38" t="n">
-        <v>92.52733305474966</v>
+        <v>326.7932120794853</v>
       </c>
       <c r="E38" t="n">
-        <v>92.52733305474966</v>
+        <v>245.6181720725473</v>
       </c>
       <c r="F38" t="n">
-        <v>92.52733305474966</v>
+        <v>163.9114764078889</v>
       </c>
       <c r="G38" t="n">
-        <v>13.28</v>
+        <v>84.66414335313922</v>
       </c>
       <c r="H38" t="n">
         <v>13.28</v>
@@ -7174,7 +7174,7 @@
         <v>416.3986957771596</v>
       </c>
       <c r="M38" t="n">
-        <v>416.3986957771596</v>
+        <v>351.9412644461907</v>
       </c>
       <c r="N38" t="n">
         <v>351.9412644461907</v>
@@ -7198,19 +7198,19 @@
         <v>664</v>
       </c>
       <c r="U38" t="n">
-        <v>664</v>
+        <v>613.1304759164232</v>
       </c>
       <c r="V38" t="n">
-        <v>664</v>
+        <v>613.1304759164232</v>
       </c>
       <c r="W38" t="n">
-        <v>546.5413645684557</v>
+        <v>613.1304759164232</v>
       </c>
       <c r="X38" t="n">
-        <v>546.5413645684557</v>
+        <v>613.1304759164232</v>
       </c>
       <c r="Y38" t="n">
-        <v>378.8645968916875</v>
+        <v>613.1304759164232</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>68.00080854584176</v>
+        <v>112.0941563582309</v>
       </c>
       <c r="C39" t="n">
-        <v>30.52614950996369</v>
+        <v>74.61949732235281</v>
       </c>
       <c r="D39" t="n">
-        <v>30.52614950996369</v>
+        <v>50.44001560750166</v>
       </c>
       <c r="E39" t="n">
-        <v>30.52614950996369</v>
+        <v>31.57931134294346</v>
       </c>
       <c r="F39" t="n">
-        <v>14.73196533029008</v>
+        <v>15.78512716326985</v>
       </c>
       <c r="G39" t="n">
-        <v>14.73196533029008</v>
+        <v>14.73196533029007</v>
       </c>
       <c r="H39" t="n">
         <v>13.28</v>
@@ -7244,52 +7244,52 @@
         <v>13.28</v>
       </c>
       <c r="J39" t="n">
-        <v>13.28</v>
+        <v>177.62</v>
       </c>
       <c r="K39" t="n">
-        <v>20.96100896075475</v>
+        <v>341.96</v>
       </c>
       <c r="L39" t="n">
-        <v>96.49532621599025</v>
+        <v>386.6834009705235</v>
       </c>
       <c r="M39" t="n">
-        <v>158.0522056665272</v>
+        <v>501.3602704875763</v>
       </c>
       <c r="N39" t="n">
-        <v>310.9790600725719</v>
+        <v>501.3602704875763</v>
       </c>
       <c r="O39" t="n">
-        <v>335.3199999999999</v>
+        <v>525.7012104150043</v>
       </c>
       <c r="P39" t="n">
-        <v>499.66</v>
+        <v>664</v>
       </c>
       <c r="Q39" t="n">
         <v>664</v>
       </c>
       <c r="R39" t="n">
-        <v>496.3232323232311</v>
+        <v>664</v>
       </c>
       <c r="S39" t="n">
-        <v>391.8546641123335</v>
+        <v>664</v>
       </c>
       <c r="T39" t="n">
-        <v>312.5124960824453</v>
+        <v>584.6578319701118</v>
       </c>
       <c r="U39" t="n">
-        <v>235.5786468869069</v>
+        <v>507.7239827745735</v>
       </c>
       <c r="V39" t="n">
-        <v>144.1537305318361</v>
+        <v>416.2990664195026</v>
       </c>
       <c r="W39" t="n">
-        <v>144.1537305318361</v>
+        <v>306.8312452984637</v>
       </c>
       <c r="X39" t="n">
-        <v>144.1537305318361</v>
+        <v>249.4153173809187</v>
       </c>
       <c r="Y39" t="n">
-        <v>68.00080854584176</v>
+        <v>173.2623953949245</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>228.1448425304257</v>
+        <v>233.5123111456234</v>
       </c>
       <c r="C40" t="n">
-        <v>278.9068483488615</v>
+        <v>233.5123111456234</v>
       </c>
       <c r="D40" t="n">
-        <v>278.9068483488615</v>
+        <v>271.5914552706234</v>
       </c>
       <c r="E40" t="n">
-        <v>321.4957525602745</v>
+        <v>314.1803594820365</v>
       </c>
       <c r="F40" t="n">
-        <v>321.4957525602745</v>
+        <v>314.1803594820365</v>
       </c>
       <c r="G40" t="n">
-        <v>400.2407381192909</v>
+        <v>314.1803594820365</v>
       </c>
       <c r="H40" t="n">
-        <v>499.66</v>
+        <v>413.5996213627455</v>
       </c>
       <c r="I40" t="n">
-        <v>499.66</v>
+        <v>554.7643158522485</v>
       </c>
       <c r="J40" t="n">
         <v>664</v>
@@ -7335,40 +7335,40 @@
         <v>545.0812119029629</v>
       </c>
       <c r="N40" t="n">
-        <v>544.7864458002055</v>
+        <v>516.3103030303055</v>
       </c>
       <c r="O40" t="n">
-        <v>377.1096781234365</v>
+        <v>348.6335353535366</v>
       </c>
       <c r="P40" t="n">
-        <v>377.1096781234365</v>
+        <v>180.9567676767677</v>
       </c>
       <c r="Q40" t="n">
-        <v>209.4329104466674</v>
+        <v>180.9567676767677</v>
       </c>
       <c r="R40" t="n">
-        <v>41.75614276989868</v>
+        <v>13.28</v>
       </c>
       <c r="S40" t="n">
         <v>13.28</v>
       </c>
       <c r="T40" t="n">
-        <v>115.8367138399401</v>
+        <v>13.28</v>
       </c>
       <c r="U40" t="n">
-        <v>115.8367138399401</v>
+        <v>13.28</v>
       </c>
       <c r="V40" t="n">
-        <v>115.8367138399401</v>
+        <v>136.861392885946</v>
       </c>
       <c r="W40" t="n">
-        <v>115.8367138399401</v>
+        <v>233.5123111456234</v>
       </c>
       <c r="X40" t="n">
-        <v>191.6275048641336</v>
+        <v>233.5123111456234</v>
       </c>
       <c r="Y40" t="n">
-        <v>191.6275048641336</v>
+        <v>233.5123111456234</v>
       </c>
     </row>
     <row r="41">
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>227.212480753106</v>
+        <v>378.727632268257</v>
       </c>
       <c r="C41" t="n">
-        <v>75.69732923795442</v>
+        <v>315.0303030303049</v>
       </c>
       <c r="D41" t="n">
-        <v>75.69732923795442</v>
+        <v>315.0303030303049</v>
       </c>
       <c r="E41" t="n">
-        <v>75.69732923795442</v>
+        <v>163.5151515151532</v>
       </c>
       <c r="F41" t="n">
-        <v>75.69732923795442</v>
+        <v>163.5151515151532</v>
       </c>
       <c r="G41" t="n">
         <v>12</v>
@@ -7411,7 +7411,7 @@
         <v>383.7510581892199</v>
       </c>
       <c r="M41" t="n">
-        <v>303.7812644461907</v>
+        <v>383.7510581892199</v>
       </c>
       <c r="N41" t="n">
         <v>303.7812644461907</v>
@@ -7429,25 +7429,25 @@
         <v>530.242783783409</v>
       </c>
       <c r="S41" t="n">
-        <v>378.7276322682575</v>
+        <v>530.242783783409</v>
       </c>
       <c r="T41" t="n">
-        <v>378.7276322682575</v>
+        <v>530.242783783409</v>
       </c>
       <c r="U41" t="n">
-        <v>378.7276322682575</v>
+        <v>530.242783783409</v>
       </c>
       <c r="V41" t="n">
-        <v>378.7276322682575</v>
+        <v>530.242783783409</v>
       </c>
       <c r="W41" t="n">
-        <v>378.7276322682575</v>
+        <v>530.242783783409</v>
       </c>
       <c r="X41" t="n">
-        <v>378.7276322682575</v>
+        <v>530.242783783409</v>
       </c>
       <c r="Y41" t="n">
-        <v>227.212480753106</v>
+        <v>530.242783783409</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>145.4545454545455</v>
+        <v>106.072774008795</v>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>106.072774008795</v>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>106.072774008795</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>106.072774008795</v>
       </c>
       <c r="F42" t="n">
-        <v>12</v>
+        <v>106.072774008795</v>
       </c>
       <c r="G42" t="n">
-        <v>12</v>
+        <v>106.072774008795</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>106.072774008795</v>
       </c>
       <c r="I42" t="n">
         <v>12</v>
@@ -7484,22 +7484,22 @@
         <v>74.95030453471296</v>
       </c>
       <c r="K42" t="n">
-        <v>223.450304534713</v>
+        <v>181.6313134954677</v>
       </c>
       <c r="L42" t="n">
-        <v>260.3963211479205</v>
+        <v>317.5773301086753</v>
       </c>
       <c r="M42" t="n">
-        <v>408.8963211479205</v>
+        <v>382.9466503916103</v>
       </c>
       <c r="N42" t="n">
-        <v>424.1822293092411</v>
+        <v>531.4466503916103</v>
       </c>
       <c r="O42" t="n">
-        <v>572.6822293092411</v>
+        <v>555.7875903190384</v>
       </c>
       <c r="P42" t="n">
-        <v>600</v>
+        <v>584.2786701754238</v>
       </c>
       <c r="Q42" t="n">
         <v>600</v>
@@ -7508,25 +7508,25 @@
         <v>600</v>
       </c>
       <c r="S42" t="n">
-        <v>600</v>
+        <v>448.4848484848485</v>
       </c>
       <c r="T42" t="n">
-        <v>448.4848484848485</v>
+        <v>296.9696969696959</v>
       </c>
       <c r="U42" t="n">
-        <v>296.969696969697</v>
+        <v>145.454545454543</v>
       </c>
       <c r="V42" t="n">
-        <v>296.969696969697</v>
+        <v>106.072774008795</v>
       </c>
       <c r="W42" t="n">
-        <v>145.4545454545455</v>
+        <v>106.072774008795</v>
       </c>
       <c r="X42" t="n">
-        <v>145.4545454545455</v>
+        <v>106.072774008795</v>
       </c>
       <c r="Y42" t="n">
-        <v>145.4545454545455</v>
+        <v>106.072774008795</v>
       </c>
     </row>
     <row r="43">
@@ -7563,31 +7563,31 @@
         <v>116.9780114721234</v>
       </c>
       <c r="K43" t="n">
-        <v>116.9780114721234</v>
+        <v>12</v>
       </c>
       <c r="L43" t="n">
-        <v>116.9780114721234</v>
+        <v>12</v>
       </c>
       <c r="M43" t="n">
-        <v>116.9780114721234</v>
+        <v>12</v>
       </c>
       <c r="N43" t="n">
-        <v>116.9780114721234</v>
+        <v>12</v>
       </c>
       <c r="O43" t="n">
-        <v>116.9780114721234</v>
+        <v>12</v>
       </c>
       <c r="P43" t="n">
-        <v>116.9780114721234</v>
+        <v>12</v>
       </c>
       <c r="Q43" t="n">
-        <v>116.9780114721234</v>
+        <v>12</v>
       </c>
       <c r="R43" t="n">
-        <v>116.9780114721234</v>
+        <v>12</v>
       </c>
       <c r="S43" t="n">
-        <v>116.9780114721234</v>
+        <v>12</v>
       </c>
       <c r="T43" t="n">
         <v>12</v>
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>520</v>
+        <v>98.14347889373249</v>
       </c>
       <c r="C44" t="n">
-        <v>520</v>
+        <v>98.14347889373249</v>
       </c>
       <c r="D44" t="n">
-        <v>388.6868686868687</v>
+        <v>98.14347889373249</v>
       </c>
       <c r="E44" t="n">
-        <v>360.7697415199951</v>
+        <v>98.14347889373249</v>
       </c>
       <c r="F44" t="n">
-        <v>229.4566102068638</v>
+        <v>98.14347889373249</v>
       </c>
       <c r="G44" t="n">
         <v>98.14347889373249</v>
@@ -7663,28 +7663,28 @@
         <v>520</v>
       </c>
       <c r="R44" t="n">
-        <v>520</v>
+        <v>388.6868686868687</v>
       </c>
       <c r="S44" t="n">
-        <v>520</v>
+        <v>388.6868686868687</v>
       </c>
       <c r="T44" t="n">
-        <v>520</v>
+        <v>360.7697415199951</v>
       </c>
       <c r="U44" t="n">
-        <v>520</v>
+        <v>360.7697415199951</v>
       </c>
       <c r="V44" t="n">
-        <v>520</v>
+        <v>360.7697415199951</v>
       </c>
       <c r="W44" t="n">
-        <v>520</v>
+        <v>229.4566102068638</v>
       </c>
       <c r="X44" t="n">
-        <v>520</v>
+        <v>98.14347889373249</v>
       </c>
       <c r="Y44" t="n">
-        <v>520</v>
+        <v>98.14347889373249</v>
       </c>
     </row>
     <row r="45">
@@ -7694,46 +7694,46 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10.4</v>
+        <v>141.7131313131313</v>
       </c>
       <c r="C45" t="n">
-        <v>10.4</v>
+        <v>141.7131313131313</v>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>141.7131313131313</v>
       </c>
       <c r="E45" t="n">
-        <v>10.4</v>
+        <v>141.7131313131313</v>
       </c>
       <c r="F45" t="n">
-        <v>10.4</v>
+        <v>141.7131313131313</v>
       </c>
       <c r="G45" t="n">
-        <v>10.4</v>
+        <v>141.7131313131313</v>
       </c>
       <c r="H45" t="n">
-        <v>10.4</v>
+        <v>141.7131313131313</v>
       </c>
       <c r="I45" t="n">
         <v>10.4</v>
       </c>
       <c r="J45" t="n">
-        <v>10.4</v>
+        <v>35.95028042105832</v>
       </c>
       <c r="K45" t="n">
-        <v>139.1</v>
+        <v>56.50128938181308</v>
       </c>
       <c r="L45" t="n">
-        <v>267.8</v>
+        <v>185.2012893818131</v>
       </c>
       <c r="M45" t="n">
-        <v>339.6412893818131</v>
+        <v>313.9012893818131</v>
       </c>
       <c r="N45" t="n">
-        <v>468.3412893818131</v>
+        <v>442.601289381813</v>
       </c>
       <c r="O45" t="n">
-        <v>492.6822293092411</v>
+        <v>479.812229309241</v>
       </c>
       <c r="P45" t="n">
         <v>520</v>
@@ -7742,28 +7742,28 @@
         <v>448.1617486221571</v>
       </c>
       <c r="R45" t="n">
-        <v>316.8486173090258</v>
+        <v>448.1617486221571</v>
       </c>
       <c r="S45" t="n">
-        <v>185.5354859958945</v>
+        <v>404.339393939394</v>
       </c>
       <c r="T45" t="n">
-        <v>185.5354859958945</v>
+        <v>404.339393939394</v>
       </c>
       <c r="U45" t="n">
-        <v>185.5354859958945</v>
+        <v>404.339393939394</v>
       </c>
       <c r="V45" t="n">
-        <v>54.22235468276318</v>
+        <v>404.339393939394</v>
       </c>
       <c r="W45" t="n">
-        <v>10.4</v>
+        <v>273.0262626262627</v>
       </c>
       <c r="X45" t="n">
-        <v>10.4</v>
+        <v>273.0262626262627</v>
       </c>
       <c r="Y45" t="n">
-        <v>10.4</v>
+        <v>273.0262626262627</v>
       </c>
     </row>
     <row r="46">
@@ -7830,19 +7830,19 @@
         <v>29.24801147212342</v>
       </c>
       <c r="U46" t="n">
-        <v>10.4</v>
+        <v>29.24801147212342</v>
       </c>
       <c r="V46" t="n">
-        <v>10.4</v>
+        <v>29.24801147212342</v>
       </c>
       <c r="W46" t="n">
-        <v>10.4</v>
+        <v>29.24801147212342</v>
       </c>
       <c r="X46" t="n">
-        <v>10.4</v>
+        <v>29.24801147212342</v>
       </c>
       <c r="Y46" t="n">
-        <v>10.4</v>
+        <v>29.24801147212342</v>
       </c>
     </row>
   </sheetData>
@@ -7961,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>120.6470157237802</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>181.0255281878544</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
         <v>32.16598080989746</v>
       </c>
       <c r="R2" t="n">
-        <v>294.54111633436</v>
+        <v>75.55501084372705</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -8043,7 +8043,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>36.41383380332024</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -8052,13 +8052,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>208.1647782656032</v>
       </c>
       <c r="N3" t="n">
-        <v>43.51606291851528</v>
+        <v>303.9644313485227</v>
       </c>
       <c r="O3" t="n">
-        <v>134.4360014556385</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -8210,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>315.5523185970912</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>150.2199033577513</v>
+        <v>181.0255281878544</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>32.16598080989746</v>
       </c>
       <c r="R5" t="n">
-        <v>63.60076038878513</v>
+        <v>127.8155776702147</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -8277,10 +8277,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>17.72758189252907</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>170.8498352589587</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -8289,7 +8289,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>208.1647782656032</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>244.8383852055136</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -8459,10 +8459,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.16598080989746</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>63.60076038878515</v>
+        <v>288.7465198414795</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>208.1647782656032</v>
       </c>
       <c r="N9" t="n">
-        <v>72.17123455344384</v>
+        <v>303.9644313485227</v>
       </c>
       <c r="O9" t="n">
-        <v>134.4360014556385</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>192.6007603887851</v>
+        <v>274.7974090643714</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -8766,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>71.32192874183379</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -8833,7 +8833,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J13" t="n">
-        <v>134.2003162992274</v>
+        <v>18.10301740934398</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -8936,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>166.4731478460166</v>
+        <v>166.4731478460165</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.811941199415047</v>
+        <v>3.811941199414852</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>166.4691155319637</v>
+        <v>166.4691155319641</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -9869,7 +9869,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>133.3810520646158</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -9936,13 +9936,13 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>17.72758189252907</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>16.57517358953142</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>114.2151256828663</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -9957,10 +9957,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>138.4062922315566</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -10018,7 +10018,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J28" t="n">
-        <v>39.1619208728401</v>
+        <v>134.2003162992274</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>182.7183877936346</v>
+        <v>229.9183739766696</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -10252,10 +10252,10 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>22.34630454117203</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>134.2003162992274</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -10358,7 +10358,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>138.6007603887851</v>
+        <v>288.4831980972736</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>17.72758189252907</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>175.0441903109148</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -10489,10 +10489,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>22.34630454117203</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>134.2003162992274</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -10583,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>117.7164568985914</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,10 +10592,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>32.16598080989746</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>138.6007603887851</v>
+        <v>227.8159155082058</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -10668,7 +10668,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>113.894238068156</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -10890,13 +10890,13 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>158.2414050901467</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>270.3434443772567</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -10905,7 +10905,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>112.1020392871078</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -11054,10 +11054,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>136.3822227914923</v>
+        <v>315.5523185970912</v>
       </c>
       <c r="N41" t="n">
-        <v>144.8383852055136</v>
+        <v>65.66828939991473</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11127,25 +11127,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>142.2414050901467</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>358.1647782656032</v>
+        <v>274.1943947130123</v>
       </c>
       <c r="N42" t="n">
-        <v>171.519429450189</v>
+        <v>319.5284298928841</v>
       </c>
       <c r="O42" t="n">
-        <v>125.4131919924969</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.395064207597855</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -11291,10 +11291,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>303.5322180945786</v>
+        <v>315.5523185970912</v>
       </c>
       <c r="N44" t="n">
-        <v>152.6868375981859</v>
+        <v>165.6868375981859</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>19.16598080989746</v>
+        <v>32.16598080989746</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,19 +11361,19 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>36.41383380332024</v>
+        <v>55.84483937442928</v>
       </c>
       <c r="K45" t="n">
-        <v>122.2414050901467</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>92.68079129979034</v>
+        <v>79.68079129979034</v>
       </c>
       <c r="M45" t="n">
-        <v>280.7317372371315</v>
+        <v>338.1647782656032</v>
       </c>
       <c r="N45" t="n">
-        <v>299.5284298928841</v>
+        <v>286.5284298928841</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -22524,7 +22524,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -22566,19 +22566,19 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>14.97383298484527</v>
+        <v>82.55939203153169</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1170955435855</v>
+        <v>83.11709554358555</v>
       </c>
       <c r="V2" t="n">
-        <v>220.3268989659476</v>
+        <v>63.85102416682389</v>
       </c>
       <c r="W2" t="n">
-        <v>72.37347598094755</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>26.28183346066771</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -22749,16 +22749,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
@@ -22800,22 +22800,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>32.72665518420583</v>
       </c>
       <c r="T5" t="n">
-        <v>180.9738329848453</v>
+        <v>14.97383298484529</v>
       </c>
       <c r="U5" t="n">
-        <v>83.11709554358553</v>
+        <v>249.1170955435855</v>
       </c>
       <c r="V5" t="n">
-        <v>229.8510241668239</v>
+        <v>63.85102416682389</v>
       </c>
       <c r="W5" t="n">
-        <v>85.27646771044027</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>192.2818334606677</v>
+        <v>26.28183346066771</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>29.04584091074662</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -22949,13 +22949,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>144.2109825806168</v>
+        <v>50.78402847581849</v>
       </c>
       <c r="Q7" t="n">
         <v>110.915266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>134.3315706041019</v>
+        <v>256.8043656196468</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>72.4751877546982</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -23040,16 +23040,16 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>180.9738329848453</v>
+        <v>14.97383298484527</v>
       </c>
       <c r="U8" t="n">
         <v>83.11709554358555</v>
       </c>
       <c r="V8" t="n">
-        <v>63.85102416682389</v>
+        <v>136.3262119215221</v>
       </c>
       <c r="W8" t="n">
-        <v>72.37347598094755</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
@@ -23229,19 +23229,19 @@
         <v>178.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>139.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>133.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>133.8896287080119</v>
       </c>
       <c r="G11" t="n">
         <v>131.4548597242022</v>
       </c>
       <c r="H11" t="n">
-        <v>111.3471306276197</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,25 +23274,25 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>28.16716277719729</v>
+        <v>144.9638204366549</v>
       </c>
       <c r="T11" t="n">
         <v>309.9738329848453</v>
       </c>
       <c r="U11" t="n">
-        <v>378.1170955435855</v>
+        <v>212.1170955435855</v>
       </c>
       <c r="V11" t="n">
-        <v>192.8510241668239</v>
+        <v>358.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>367.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>155.2818334606677</v>
+        <v>321.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>240.3174326828064</v>
+        <v>74.31743268280638</v>
       </c>
     </row>
     <row r="12">
@@ -23308,19 +23308,19 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>76.93768689770263</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>71.67209722191262</v>
+        <v>19.65198689582849</v>
       </c>
       <c r="F12" t="n">
         <v>68.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>54.04263021464999</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>54.43744567698718</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -23356,7 +23356,7 @@
         <v>182.6192829834793</v>
       </c>
       <c r="T12" t="n">
-        <v>2.985764588139688</v>
+        <v>131.5487463495893</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -23414,22 +23414,22 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>158.0458409107466</v>
       </c>
       <c r="N13" t="n">
         <v>210.7770096979144</v>
       </c>
       <c r="O13" t="n">
-        <v>286.8627444068838</v>
+        <v>120.8627444068838</v>
       </c>
       <c r="P13" t="n">
-        <v>338.492210034085</v>
+        <v>179.7840284758185</v>
       </c>
       <c r="Q13" t="n">
-        <v>239.915266425598</v>
+        <v>240.5776070731179</v>
       </c>
       <c r="R13" t="n">
-        <v>263.3315706041019</v>
+        <v>429.3315706041019</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -23466,7 +23466,7 @@
         <v>149.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>110.3391557398498</v>
       </c>
       <c r="E14" t="n">
         <v>104.3632896068686</v>
@@ -23478,7 +23478,7 @@
         <v>102.4548597242021</v>
       </c>
       <c r="H14" t="n">
-        <v>57.96382043665496</v>
+        <v>94.67030191960782</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,16 +23511,16 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>18.95436277719734</v>
       </c>
       <c r="T14" t="n">
         <v>114.9738329848453</v>
       </c>
       <c r="U14" t="n">
-        <v>349.1170955435855</v>
+        <v>183.1170955435855</v>
       </c>
       <c r="V14" t="n">
-        <v>329.8510241668239</v>
+        <v>163.8510241668239</v>
       </c>
       <c r="W14" t="n">
         <v>338.3734759809475</v>
@@ -23529,7 +23529,7 @@
         <v>292.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>45.31743268280638</v>
+        <v>211.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -23539,10 +23539,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>84.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>61.09991244551929</v>
+        <v>19.58060405934275</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -23551,10 +23551,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>39.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>25.04263021464999</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -23596,19 +23596,19 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>100.164510703583</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>114.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>25.68628233925462</v>
+        <v>132.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>99.39139276613435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -23651,22 +23651,22 @@
         <v>36.68375930532015</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>129.0458409107466</v>
       </c>
       <c r="N16" t="n">
         <v>181.7770096979144</v>
       </c>
       <c r="O16" t="n">
-        <v>91.86274440688379</v>
+        <v>163.8413257490835</v>
       </c>
       <c r="P16" t="n">
         <v>150.7840284758185</v>
       </c>
       <c r="Q16" t="n">
-        <v>376.915266425598</v>
+        <v>210.915266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>269.3559928570482</v>
+        <v>234.3315706041019</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -23697,13 +23697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>180.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>148.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>109.3391557398498</v>
+        <v>96.50744693841823</v>
       </c>
       <c r="E17" t="n">
         <v>103.3632896068686</v>
@@ -23748,16 +23748,16 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>164.1671627771973</v>
       </c>
       <c r="T17" t="n">
-        <v>97.97383298484529</v>
+        <v>279.9738329848453</v>
       </c>
       <c r="U17" t="n">
-        <v>348.1170955435855</v>
+        <v>166.1170955435855</v>
       </c>
       <c r="V17" t="n">
-        <v>150.7125869440212</v>
+        <v>328.8510241668239</v>
       </c>
       <c r="W17" t="n">
         <v>337.3734759809475</v>
@@ -23776,10 +23776,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>83.55655664632661</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>60.09991244551929</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -23791,10 +23791,10 @@
         <v>38.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>24.04263021464999</v>
       </c>
       <c r="H18" t="n">
-        <v>24.43744567698717</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23827,10 +23827,10 @@
         <v>203.0045142735113</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>152.6192829834792</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>101.5487463495893</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -23839,13 +23839,13 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>131.3731429098285</v>
+        <v>111.7005519049019</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>90.44415377395885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -23888,25 +23888,25 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>128.0458409107466</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>256.8627444068838</v>
+        <v>74.86274440688379</v>
       </c>
       <c r="P19" t="n">
-        <v>241.1305788212528</v>
+        <v>135.9850383897996</v>
       </c>
       <c r="Q19" t="n">
-        <v>193.915266425598</v>
+        <v>375.915266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>217.3315706041019</v>
+        <v>399.3315706041019</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>51.1913813421997</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23940,16 +23940,16 @@
         <v>148.4745782429939</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>109.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>103.3632896068686</v>
       </c>
       <c r="F20" t="n">
         <v>103.8896287080119</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>101.4548597242022</v>
       </c>
       <c r="H20" t="n">
         <v>93.67030191960782</v>
@@ -23988,22 +23988,22 @@
         <v>164.1671627771973</v>
       </c>
       <c r="T20" t="n">
-        <v>77.97383298484328</v>
+        <v>279.9738329848453</v>
       </c>
       <c r="U20" t="n">
         <v>348.1170955435855</v>
       </c>
       <c r="V20" t="n">
-        <v>328.8510241668239</v>
+        <v>126.8510241668225</v>
       </c>
       <c r="W20" t="n">
         <v>337.3734759809475</v>
       </c>
       <c r="X20" t="n">
-        <v>291.2818334606677</v>
+        <v>92.35954641624429</v>
       </c>
       <c r="Y20" t="n">
-        <v>123.5524507093035</v>
+        <v>8.317432682805475</v>
       </c>
     </row>
     <row r="21">
@@ -24013,16 +24013,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>83.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>60.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>46.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>41.67209722191262</v>
       </c>
       <c r="F21" t="n">
         <v>38.63624233787687</v>
@@ -24064,7 +24064,7 @@
         <v>203.0045142735113</v>
       </c>
       <c r="S21" t="n">
-        <v>152.6192829834793</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -24079,10 +24079,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>111.195852577504</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>31.54888234952183</v>
       </c>
     </row>
     <row r="22">
@@ -24122,7 +24122,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>35.68375930532017</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>128.0458409107466</v>
@@ -24131,13 +24131,13 @@
         <v>180.7770096979144</v>
       </c>
       <c r="O22" t="n">
-        <v>130.1325257490864</v>
+        <v>165.8162850544037</v>
       </c>
       <c r="P22" t="n">
-        <v>113.784028475817</v>
+        <v>113.7840284758184</v>
       </c>
       <c r="Q22" t="n">
-        <v>173.9152664255969</v>
+        <v>173.9152664255979</v>
       </c>
       <c r="R22" t="n">
         <v>197.3315706041018</v>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>179.9993129555745</v>
       </c>
       <c r="C23" t="n">
         <v>147.4745782429939</v>
@@ -24183,13 +24183,13 @@
         <v>102.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>102.8896287080119</v>
       </c>
       <c r="G23" t="n">
         <v>100.4548597242021</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>92.67030191960782</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24225,19 +24225,19 @@
         <v>163.1671627771973</v>
       </c>
       <c r="T23" t="n">
-        <v>72.97383298484328</v>
+        <v>278.9738329848453</v>
       </c>
       <c r="U23" t="n">
-        <v>335.2315391267824</v>
+        <v>141.1170955435841</v>
       </c>
       <c r="V23" t="n">
-        <v>327.8510241668239</v>
+        <v>121.851024166823</v>
       </c>
       <c r="W23" t="n">
-        <v>130.3734759809468</v>
+        <v>154.9286759809502</v>
       </c>
       <c r="X23" t="n">
-        <v>290.2818334606677</v>
+        <v>84.28183346066726</v>
       </c>
       <c r="Y23" t="n">
         <v>209.3174326828064</v>
@@ -24262,13 +24262,13 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>37.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>23.04263021464999</v>
       </c>
       <c r="H24" t="n">
-        <v>23.43744567698717</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24298,28 +24298,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>202.0045142735113</v>
       </c>
       <c r="S24" t="n">
         <v>151.6192829834792</v>
       </c>
       <c r="T24" t="n">
-        <v>100.5487463495893</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>16.37319768253923</v>
       </c>
       <c r="W24" t="n">
-        <v>112.7796579499416</v>
+        <v>130.3731429098285</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>97.39139276613435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24374,13 +24374,13 @@
         <v>108.7840284758184</v>
       </c>
       <c r="Q25" t="n">
-        <v>370.7076886785443</v>
+        <v>320.5163073363446</v>
       </c>
       <c r="R25" t="n">
         <v>192.3315706041018</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>50.1913813421997</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24408,25 +24408,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>60.99931295557326</v>
+        <v>226.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>28.47457824299249</v>
+        <v>194.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>155.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>149.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>149.8896287080119</v>
+        <v>114.1411460916717</v>
       </c>
       <c r="G26" t="n">
-        <v>147.4548597242022</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>139.6703019196078</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24465,7 +24465,7 @@
         <v>325.9738329848453</v>
       </c>
       <c r="U26" t="n">
-        <v>394.1170955435855</v>
+        <v>228.1170955435855</v>
       </c>
       <c r="V26" t="n">
         <v>374.8510241668239</v>
@@ -24474,7 +24474,7 @@
         <v>383.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>174.4323230675391</v>
+        <v>337.2818334606677</v>
       </c>
       <c r="Y26" t="n">
         <v>256.3174326828064</v>
@@ -24535,28 +24535,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>240.3296316140031</v>
+        <v>83.00451427350947</v>
       </c>
       <c r="S27" t="n">
-        <v>198.6192829834792</v>
+        <v>32.61928298347766</v>
       </c>
       <c r="T27" t="n">
         <v>147.5487463495893</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>145.164510703583</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>157.6892599576588</v>
       </c>
       <c r="W27" t="n">
-        <v>11.37314290982749</v>
+        <v>11.37314290982772</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>164.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>144.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -24572,10 +24572,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>30.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>25.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -24599,16 +24599,16 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>8.045840910745028</v>
+        <v>8.04584091074662</v>
       </c>
       <c r="N28" t="n">
-        <v>139.441661976691</v>
+        <v>159.6155190608617</v>
       </c>
       <c r="O28" t="n">
         <v>302.8627444068838</v>
       </c>
       <c r="P28" t="n">
-        <v>195.7840284758166</v>
+        <v>361.7840284758185</v>
       </c>
       <c r="Q28" t="n">
         <v>421.915266425598</v>
@@ -24617,7 +24617,7 @@
         <v>445.3315706041019</v>
       </c>
       <c r="S28" t="n">
-        <v>97.1913813421997</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24635,7 +24635,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>32.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -24657,13 +24657,13 @@
         <v>91.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>91.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>89.45485972420214</v>
       </c>
       <c r="H29" t="n">
-        <v>81.67030191960782</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24702,7 +24702,7 @@
         <v>267.9738329848453</v>
       </c>
       <c r="U29" t="n">
-        <v>181.1728892506314</v>
+        <v>336.1170955435855</v>
       </c>
       <c r="V29" t="n">
         <v>316.8510241668239</v>
@@ -24714,7 +24714,7 @@
         <v>279.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>198.3174326828064</v>
+        <v>127.4782972932698</v>
       </c>
     </row>
     <row r="30">
@@ -24724,16 +24724,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>71.55655664632661</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>34.93768689770263</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>29.67209722191262</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -24772,10 +24772,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>191.0045142735113</v>
+        <v>66.03229553632727</v>
       </c>
       <c r="S30" t="n">
-        <v>94.44843468127263</v>
+        <v>140.6192829834792</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -24787,10 +24787,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>119.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>106.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>86.39139276613435</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>23.68375930532015</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24845,13 +24845,13 @@
         <v>78.86274440688379</v>
       </c>
       <c r="P31" t="n">
-        <v>297.3008286918853</v>
+        <v>137.7840284758185</v>
       </c>
       <c r="Q31" t="n">
-        <v>363.915266425598</v>
+        <v>333.7483073363447</v>
       </c>
       <c r="R31" t="n">
-        <v>221.3315706041019</v>
+        <v>387.3315706041019</v>
       </c>
       <c r="S31" t="n">
         <v>39.1913813421997</v>
@@ -24888,19 +24888,19 @@
         <v>124.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>85.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>79.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>77.45485972420214</v>
+        <v>77.45485972420215</v>
       </c>
       <c r="H32" t="n">
-        <v>69.67030191960782</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24939,19 +24939,19 @@
         <v>255.9738329848453</v>
       </c>
       <c r="U32" t="n">
-        <v>158.1170955435842</v>
+        <v>158.1170955435845</v>
       </c>
       <c r="V32" t="n">
-        <v>238.0015137736954</v>
+        <v>140.9006001411632</v>
       </c>
       <c r="W32" t="n">
-        <v>147.3734759809469</v>
+        <v>313.3734759809475</v>
       </c>
       <c r="X32" t="n">
         <v>267.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>20.31743268280559</v>
+        <v>186.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -24964,16 +24964,16 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>36.09991244551929</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>22.93768689770263</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>17.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>14.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -25009,10 +25009,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>13.00451427351061</v>
+        <v>179.0045142735113</v>
       </c>
       <c r="S33" t="n">
-        <v>128.6192829834792</v>
+        <v>128.6192829834793</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -25024,10 +25024,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>5.812292458619879</v>
+        <v>26.02097080701805</v>
       </c>
       <c r="X33" t="n">
-        <v>94.86273944538755</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -25070,28 +25070,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>11.68375930532015</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>104.0458409107466</v>
       </c>
       <c r="N34" t="n">
-        <v>10.56420969791738</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>232.8627444068838</v>
       </c>
       <c r="P34" t="n">
-        <v>125.7840284758173</v>
+        <v>175.2233788212537</v>
       </c>
       <c r="Q34" t="n">
         <v>185.915266425597</v>
       </c>
       <c r="R34" t="n">
-        <v>209.3315706041011</v>
+        <v>209.3315706041019</v>
       </c>
       <c r="S34" t="n">
-        <v>27.1913813421997</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25128,7 +25128,7 @@
         <v>85.33915573984979</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>79.36328960686865</v>
       </c>
       <c r="F35" t="n">
         <v>79.88962870801186</v>
@@ -25137,7 +25137,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>69.67030191960782</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25170,22 +25170,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>140.1671627771973</v>
       </c>
       <c r="T35" t="n">
-        <v>89.97383298484408</v>
+        <v>255.9738329848453</v>
       </c>
       <c r="U35" t="n">
-        <v>158.1170955435842</v>
+        <v>324.1170955435855</v>
       </c>
       <c r="V35" t="n">
-        <v>304.8510241668239</v>
+        <v>138.8510241668235</v>
       </c>
       <c r="W35" t="n">
-        <v>298.1459880892182</v>
+        <v>147.3734759809473</v>
       </c>
       <c r="X35" t="n">
-        <v>267.2818334606677</v>
+        <v>102.1941951044782</v>
       </c>
       <c r="Y35" t="n">
         <v>186.3174326828064</v>
@@ -25204,10 +25204,10 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>22.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>17.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -25249,22 +25249,22 @@
         <v>179.0045142735113</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>128.6192829834793</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>75.16451070358295</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.083283909315455</v>
       </c>
       <c r="X36" t="n">
-        <v>61.8036458650018</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -25313,22 +25313,22 @@
         <v>104.0458409107466</v>
       </c>
       <c r="N37" t="n">
-        <v>49.43935034543743</v>
+        <v>156.7770096979144</v>
       </c>
       <c r="O37" t="n">
-        <v>66.86274440688283</v>
+        <v>98.33370371220607</v>
       </c>
       <c r="P37" t="n">
-        <v>291.7840284758184</v>
+        <v>125.7840284758175</v>
       </c>
       <c r="Q37" t="n">
-        <v>185.9152664255965</v>
+        <v>185.915266425597</v>
       </c>
       <c r="R37" t="n">
-        <v>209.3315706041011</v>
+        <v>209.3315706041019</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>27.19138134219969</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25365,16 +25365,16 @@
         <v>86.33915573984979</v>
       </c>
       <c r="E38" t="n">
-        <v>80.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>80.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>70.67030191960782</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25413,19 +25413,19 @@
         <v>256.9738329848453</v>
       </c>
       <c r="U38" t="n">
-        <v>325.1170955435855</v>
+        <v>274.7562667008445</v>
       </c>
       <c r="V38" t="n">
         <v>305.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>198.0894269037187</v>
+        <v>314.3734759809475</v>
       </c>
       <c r="X38" t="n">
         <v>268.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>21.31743268280582</v>
+        <v>187.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -25435,22 +25435,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>60.55655664632661</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>23.93768689770263</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>18.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1.042630214649989</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -25483,10 +25483,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>14.00451427351015</v>
+        <v>180.0045142735113</v>
       </c>
       <c r="S39" t="n">
-        <v>26.19540045469061</v>
+        <v>129.6192829834792</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -25498,10 +25498,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>108.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>95.86273944538755</v>
+        <v>39.02097080701806</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -25550,22 +25550,22 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>157.4851912561845</v>
+        <v>129.2938099139836</v>
       </c>
       <c r="O40" t="n">
         <v>67.8627444068826</v>
       </c>
       <c r="P40" t="n">
-        <v>292.7840284758184</v>
+        <v>126.7840284758173</v>
       </c>
       <c r="Q40" t="n">
-        <v>186.9152664255965</v>
+        <v>352.915266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>210.3315706041009</v>
+        <v>210.3315706041019</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>28.1913813421997</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,22 +25593,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>381.9993129555745</v>
+        <v>231.9993129555741</v>
       </c>
       <c r="C41" t="n">
-        <v>199.4745782429939</v>
+        <v>286.4142222974213</v>
       </c>
       <c r="D41" t="n">
         <v>310.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>304.3632896068686</v>
+        <v>154.3632896068685</v>
       </c>
       <c r="F41" t="n">
         <v>304.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>239.3945037786273</v>
+        <v>152.4548597242004</v>
       </c>
       <c r="H41" t="n">
         <v>294.6703019196078</v>
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>215.1671627771973</v>
+        <v>365.1671627771973</v>
       </c>
       <c r="T41" t="n">
         <v>480.9738329848453</v>
@@ -25662,7 +25662,7 @@
         <v>492.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>261.3174326828064</v>
+        <v>411.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25675,7 +25675,7 @@
         <v>284.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>128.9799124455193</v>
+        <v>261.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>247.9376868977026</v>
@@ -25693,7 +25693,7 @@
         <v>225.4374456769872</v>
       </c>
       <c r="I42" t="n">
-        <v>93.13204626870701</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25723,19 +25723,19 @@
         <v>404.0045142735113</v>
       </c>
       <c r="S42" t="n">
-        <v>353.6192829834793</v>
+        <v>203.6192829834792</v>
       </c>
       <c r="T42" t="n">
-        <v>152.5487463495893</v>
+        <v>152.5487463495882</v>
       </c>
       <c r="U42" t="n">
-        <v>150.164510703583</v>
+        <v>150.1645107035816</v>
       </c>
       <c r="V42" t="n">
-        <v>314.5106671915202</v>
+        <v>275.5227134602296</v>
       </c>
       <c r="W42" t="n">
-        <v>182.3731429098285</v>
+        <v>332.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>319.8627394453875</v>
@@ -25778,7 +25778,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>120.6401180634381</v>
+        <v>16.71188670603593</v>
       </c>
       <c r="L43" t="n">
         <v>236.6837593053202</v>
@@ -25805,7 +25805,7 @@
         <v>252.1913813421997</v>
       </c>
       <c r="T43" t="n">
-        <v>3.599941706232556</v>
+        <v>107.5281730636348</v>
       </c>
       <c r="U43" t="n">
         <v>50.92652242199892</v>
@@ -25836,16 +25836,16 @@
         <v>436.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>267.3391557398498</v>
+        <v>397.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>363.7253337116638</v>
+        <v>391.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>261.8896287080119</v>
+        <v>391.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>259.4548597242022</v>
+        <v>389.4548597242022</v>
       </c>
       <c r="H44" t="n">
         <v>381.6703019196078</v>
@@ -25878,13 +25878,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>156.0596440544251</v>
+        <v>26.05964405442512</v>
       </c>
       <c r="S44" t="n">
         <v>452.1671627771973</v>
       </c>
       <c r="T44" t="n">
-        <v>567.9738329848453</v>
+        <v>540.3358770896405</v>
       </c>
       <c r="U44" t="n">
         <v>636.1170955435855</v>
@@ -25893,10 +25893,10 @@
         <v>616.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>625.3734759809475</v>
+        <v>495.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>579.2818334606677</v>
+        <v>449.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>498.3174326828064</v>
@@ -25909,7 +25909,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>371.5565566463266</v>
+        <v>241.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>348.0999124455193</v>
@@ -25930,7 +25930,7 @@
         <v>312.4374456769872</v>
       </c>
       <c r="I45" t="n">
-        <v>180.132046268707</v>
+        <v>50.13204626870701</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25957,10 +25957,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>361.0045142735113</v>
+        <v>491.0045142735113</v>
       </c>
       <c r="S45" t="n">
-        <v>310.6192829834793</v>
+        <v>397.2351518475438</v>
       </c>
       <c r="T45" t="n">
         <v>389.5487463495893</v>
@@ -25969,10 +25969,10 @@
         <v>387.1645107035829</v>
       </c>
       <c r="V45" t="n">
-        <v>271.5106671915202</v>
+        <v>401.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>375.989011773893</v>
+        <v>289.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>406.8627394453875</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>274.1138003370787</v>
+        <v>255.4542689796765</v>
       </c>
       <c r="C46" t="n">
         <v>259.7252466480447</v>
@@ -26045,7 +26045,7 @@
         <v>194.5281730636348</v>
       </c>
       <c r="U46" t="n">
-        <v>119.2669910645967</v>
+        <v>137.9265224219989</v>
       </c>
       <c r="V46" t="n">
         <v>186.1703102162162</v>
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3150796.210396585</v>
+        <v>3150796.210396584</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3986312.320133872</v>
+        <v>3986312.320133871</v>
       </c>
     </row>
     <row r="6">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6711877.697866334</v>
+        <v>6711877.697866333</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7637115.119920317</v>
+        <v>7637115.119920316</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8469439.186859678</v>
+        <v>8469439.186859677</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9383220.853128787</v>
+        <v>9383220.853128785</v>
       </c>
     </row>
     <row r="12">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12215780.89129268</v>
+        <v>12215780.89129267</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12760826.93822192</v>
+        <v>12760826.93822191</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13062310.77881001</v>
+        <v>13062310.77881</v>
       </c>
     </row>
   </sheetData>
@@ -26278,40 +26278,40 @@
         <v>1039090.778098773</v>
       </c>
       <c r="E2" t="n">
-        <v>851906.4927212995</v>
+        <v>851906.4927212992</v>
       </c>
       <c r="F2" t="n">
-        <v>901194.8927212991</v>
+        <v>901194.8927212993</v>
       </c>
       <c r="G2" t="n">
-        <v>910826.8479212992</v>
+        <v>910826.8479212993</v>
       </c>
       <c r="H2" t="n">
         <v>920742.2919212998</v>
       </c>
       <c r="I2" t="n">
-        <v>924424.980721299</v>
+        <v>924424.9807212991</v>
       </c>
       <c r="J2" t="n">
-        <v>819837.1931782753</v>
+        <v>819837.1931782751</v>
       </c>
       <c r="K2" t="n">
-        <v>923289.6927212991</v>
+        <v>923289.692721299</v>
       </c>
       <c r="L2" t="n">
-        <v>943684.8927212991</v>
+        <v>943684.8927212999</v>
       </c>
       <c r="M2" t="n">
-        <v>943684.8927212993</v>
+        <v>943684.8927212998</v>
       </c>
       <c r="N2" t="n">
-        <v>941985.2927212998</v>
+        <v>941985.2927212991</v>
       </c>
       <c r="O2" t="n">
         <v>491620.2187606432</v>
       </c>
       <c r="P2" t="n">
-        <v>288297.8509538875</v>
+        <v>288297.8509538874</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>579107.902798244</v>
+        <v>579105.907746042</v>
       </c>
       <c r="C4" t="n">
-        <v>576921.852296612</v>
+        <v>576919.85724441</v>
       </c>
       <c r="D4" t="n">
-        <v>574732.8362810309</v>
+        <v>574730.841228829</v>
       </c>
       <c r="E4" t="n">
-        <v>447486.3396251175</v>
+        <v>447485.319987261</v>
       </c>
       <c r="F4" t="n">
-        <v>475595.3628818998</v>
+        <v>475594.7714311867</v>
       </c>
       <c r="G4" t="n">
-        <v>478462.6048793952</v>
+        <v>478462.0271866147</v>
       </c>
       <c r="H4" t="n">
-        <v>481938.0172745982</v>
+        <v>481937.4260386403</v>
       </c>
       <c r="I4" t="n">
-        <v>482406.6201071176</v>
+        <v>482405.9805216532</v>
       </c>
       <c r="J4" t="n">
-        <v>419998.6102524959</v>
+        <v>419997.2275559151</v>
       </c>
       <c r="K4" t="n">
-        <v>481018.3342371588</v>
+        <v>481017.5173763738</v>
       </c>
       <c r="L4" t="n">
-        <v>492840.973138907</v>
+        <v>492839.9482072862</v>
       </c>
       <c r="M4" t="n">
-        <v>490826.8694339906</v>
+        <v>490825.8445023698</v>
       </c>
       <c r="N4" t="n">
-        <v>487667.9095672386</v>
+        <v>487666.9019748542</v>
       </c>
       <c r="O4" t="n">
-        <v>223481.2384370398</v>
+        <v>223477.0513997782</v>
       </c>
       <c r="P4" t="n">
-        <v>104342.2398316312</v>
+        <v>104337.2680779013</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34867.27530052884</v>
+        <v>34869.27035273098</v>
       </c>
       <c r="C6" t="n">
-        <v>411385.3258021608</v>
+        <v>411387.3208543627</v>
       </c>
       <c r="D6" t="n">
-        <v>413574.3418177421</v>
+        <v>413576.336869944</v>
       </c>
       <c r="E6" t="n">
-        <v>147681.454096182</v>
+        <v>147682.4737340382</v>
       </c>
       <c r="F6" t="n">
-        <v>360022.8298393993</v>
+        <v>360023.4212901126</v>
       </c>
       <c r="G6" t="n">
-        <v>382498.6740419039</v>
+        <v>382499.2517346846</v>
       </c>
       <c r="H6" t="n">
-        <v>387114.7056467016</v>
+        <v>387115.2968826594</v>
       </c>
       <c r="I6" t="n">
-        <v>394833.5226141813</v>
+        <v>394834.1621996459</v>
       </c>
       <c r="J6" t="n">
-        <v>137692.9879257794</v>
+        <v>137694.3706223601</v>
       </c>
       <c r="K6" t="n">
-        <v>329201.7614841404</v>
+        <v>329202.5783449252</v>
       </c>
       <c r="L6" t="n">
-        <v>395965.4945823921</v>
+        <v>395966.5195140137</v>
       </c>
       <c r="M6" t="n">
-        <v>408379.5982873088</v>
+        <v>408380.62321893</v>
       </c>
       <c r="N6" t="n">
-        <v>409923.0271540611</v>
+        <v>409924.0347464449</v>
       </c>
       <c r="O6" t="n">
-        <v>243548.8803236033</v>
+        <v>243553.0673608649</v>
       </c>
       <c r="P6" t="n">
-        <v>167895.5141222563</v>
+        <v>167900.4858759861</v>
       </c>
     </row>
   </sheetData>
@@ -27454,7 +27454,7 @@
         <v>394.6703019196078</v>
       </c>
       <c r="I2" t="n">
-        <v>99.86604410479515</v>
+        <v>220.5130598285754</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27469,7 +27469,7 @@
         <v>315.5523185970912</v>
       </c>
       <c r="N2" t="n">
-        <v>181.0255281878544</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>169.0596440544251</v>
+        <v>388.0457495450581</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27536,7 +27536,7 @@
         <v>210.8596281612361</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>36.41383380332024</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -27545,10 +27545,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>208.1647782656032</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>126.0123669743688</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -27600,16 +27600,16 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>244.4596105464481</v>
       </c>
       <c r="H4" t="n">
-        <v>266.8841851370744</v>
+        <v>223.5765031507989</v>
       </c>
       <c r="I4" t="n">
         <v>181.4093995055526</v>
@@ -27645,10 +27645,10 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>207.5281730636348</v>
+        <v>373.5281730636348</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9265224219989</v>
+        <v>316.9265224219989</v>
       </c>
       <c r="V4" t="n">
         <v>365.1703102162162</v>
@@ -27657,7 +27657,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>358.9279560652366</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27703,10 +27703,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>315.5523185970912</v>
       </c>
       <c r="N5" t="n">
-        <v>30.80562483010311</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>400</v>
+        <v>335.7851827185705</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27770,10 +27770,10 @@
         <v>325.4374456769872</v>
       </c>
       <c r="I6" t="n">
-        <v>210.8596281612361</v>
+        <v>193.132046268707</v>
       </c>
       <c r="J6" t="n">
-        <v>36.41383380332024</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -27782,7 +27782,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>208.1647782656032</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>169.5284298928841</v>
@@ -27791,10 +27791,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>134.4360014556385</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>101.3950642075979</v>
+        <v>84.11986886406447</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27831,16 +27831,16 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>244.4596105464481</v>
@@ -27852,13 +27852,13 @@
         <v>181.4093995055526</v>
       </c>
       <c r="J7" t="n">
-        <v>157.2919999675722</v>
+        <v>294.1619208728401</v>
       </c>
       <c r="K7" t="n">
         <v>220.6401180634381</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>354.3328584758848</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>352.1913813421997</v>
       </c>
       <c r="T7" t="n">
         <v>207.5281730636348</v>
@@ -27891,13 +27891,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>392.3728098387097</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27943,7 +27943,7 @@
         <v>251.739461579432</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>244.8383852055136</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -27952,10 +27952,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>32.16598080989746</v>
       </c>
       <c r="R8" t="n">
-        <v>400</v>
+        <v>174.8542405473056</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>97.35719533944027</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -28065,16 +28065,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>291.4450789577485</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>274.3828559677419</v>
@@ -28086,16 +28086,16 @@
         <v>223.5765031507989</v>
       </c>
       <c r="I10" t="n">
-        <v>347.4093995055526</v>
+        <v>181.4093995055526</v>
       </c>
       <c r="J10" t="n">
         <v>128.1619208728401</v>
       </c>
       <c r="K10" t="n">
-        <v>386.6401180634381</v>
+        <v>220.6401180634381</v>
       </c>
       <c r="L10" t="n">
-        <v>336.6837593053202</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28125,13 +28125,13 @@
         <v>150.9265224219989</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>224.7136451973441</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>392.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>287.4653528494624</v>
@@ -28192,7 +28192,7 @@
         <v>32.16598080989746</v>
       </c>
       <c r="R11" t="n">
-        <v>271</v>
+        <v>188.8033513244137</v>
       </c>
       <c r="S11" t="n">
         <v>271</v>
@@ -28244,31 +28244,31 @@
         <v>271</v>
       </c>
       <c r="I12" t="n">
-        <v>210.8596281612361</v>
+        <v>271</v>
       </c>
       <c r="J12" t="n">
-        <v>36.41383380332024</v>
+        <v>202.4138338033202</v>
       </c>
       <c r="K12" t="n">
-        <v>158.2414050901467</v>
+        <v>3.587446226643234</v>
       </c>
       <c r="L12" t="n">
-        <v>94.38001282427618</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>208.1647782656032</v>
+        <v>271</v>
       </c>
       <c r="N12" t="n">
-        <v>98.20650115105033</v>
+        <v>271</v>
       </c>
       <c r="O12" t="n">
-        <v>141.4131919924969</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>250.1198688640645</v>
+        <v>267.3950642075978</v>
       </c>
       <c r="R12" t="n">
         <v>271</v>
@@ -28326,7 +28326,7 @@
         <v>271</v>
       </c>
       <c r="J13" t="n">
-        <v>154.9027011101166</v>
+        <v>271</v>
       </c>
       <c r="K13" t="n">
         <v>271</v>
@@ -28481,22 +28481,22 @@
         <v>300</v>
       </c>
       <c r="I15" t="n">
-        <v>213.4044192511154</v>
+        <v>300</v>
       </c>
       <c r="J15" t="n">
         <v>36.41383380332024</v>
       </c>
       <c r="K15" t="n">
-        <v>158.2414050901467</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>241.1742542341462</v>
+      </c>
+      <c r="N15" t="n">
         <v>300</v>
-      </c>
-      <c r="N15" t="n">
-        <v>169.5284298928841</v>
       </c>
       <c r="O15" t="n">
         <v>141.4131919924969</v>
@@ -28545,13 +28545,13 @@
         <v>300</v>
       </c>
       <c r="D16" t="n">
-        <v>300</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E16" t="n">
         <v>300</v>
       </c>
       <c r="F16" t="n">
-        <v>300</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G16" t="n">
         <v>300</v>
@@ -28563,10 +28563,10 @@
         <v>181.4093995055526</v>
       </c>
       <c r="J16" t="n">
-        <v>294.1619208728401</v>
+        <v>128.1619208728401</v>
       </c>
       <c r="K16" t="n">
-        <v>225.1119751463233</v>
+        <v>294.6540706955625</v>
       </c>
       <c r="L16" t="n">
         <v>300</v>
@@ -28596,7 +28596,7 @@
         <v>300</v>
       </c>
       <c r="U16" t="n">
-        <v>150.9265224219989</v>
+        <v>300</v>
       </c>
       <c r="V16" t="n">
         <v>300</v>
@@ -28608,7 +28608,7 @@
         <v>300</v>
       </c>
       <c r="Y16" t="n">
-        <v>300</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="17">
@@ -28718,31 +28718,31 @@
         <v>301</v>
       </c>
       <c r="I18" t="n">
-        <v>210.8596281612361</v>
+        <v>301</v>
       </c>
       <c r="J18" t="n">
-        <v>36.41383380332024</v>
+        <v>218.4138338033202</v>
       </c>
       <c r="K18" t="n">
-        <v>174.2414050901467</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>16.89832644341467</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>301</v>
       </c>
       <c r="N18" t="n">
-        <v>169.5284298928841</v>
+        <v>301</v>
       </c>
       <c r="O18" t="n">
-        <v>157.4131919924969</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>283.3950642075978</v>
+        <v>228.3360457877764</v>
       </c>
       <c r="R18" t="n">
         <v>301</v>
@@ -28779,7 +28779,7 @@
         <v>301</v>
       </c>
       <c r="C19" t="n">
-        <v>272.7252466480447</v>
+        <v>301</v>
       </c>
       <c r="D19" t="n">
         <v>285.5362180555555</v>
@@ -28788,22 +28788,22 @@
         <v>301</v>
       </c>
       <c r="F19" t="n">
-        <v>274.3828559677419</v>
+        <v>301</v>
       </c>
       <c r="G19" t="n">
-        <v>244.4596105464481</v>
+        <v>301</v>
       </c>
       <c r="H19" t="n">
         <v>301</v>
       </c>
       <c r="I19" t="n">
-        <v>301</v>
+        <v>205.313544459019</v>
       </c>
       <c r="J19" t="n">
-        <v>301</v>
+        <v>128.1619208728401</v>
       </c>
       <c r="K19" t="n">
-        <v>301</v>
+        <v>301.0000000000001</v>
       </c>
       <c r="L19" t="n">
         <v>301</v>
@@ -28830,16 +28830,16 @@
         <v>301</v>
       </c>
       <c r="T19" t="n">
-        <v>275.1365929725504</v>
+        <v>207.5281730636348</v>
       </c>
       <c r="U19" t="n">
-        <v>150.9265224219989</v>
+        <v>301</v>
       </c>
       <c r="V19" t="n">
         <v>301</v>
       </c>
       <c r="W19" t="n">
-        <v>226.3728098387097</v>
+        <v>301</v>
       </c>
       <c r="X19" t="n">
         <v>301</v>
@@ -28876,7 +28876,7 @@
         <v>301</v>
       </c>
       <c r="I20" t="n">
-        <v>251.8925738093141</v>
+        <v>220.5130598285754</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28900,7 +28900,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>32.16598080989746</v>
+        <v>63.54549479063644</v>
       </c>
       <c r="R20" t="n">
         <v>301</v>
@@ -28955,10 +28955,10 @@
         <v>301</v>
       </c>
       <c r="I21" t="n">
-        <v>210.8596281612361</v>
+        <v>301</v>
       </c>
       <c r="J21" t="n">
-        <v>65.82340906388932</v>
+        <v>238.4138338033203</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -28967,19 +28967,19 @@
         <v>164.6807912997904</v>
       </c>
       <c r="M21" t="n">
-        <v>208.1647782656032</v>
+        <v>301</v>
       </c>
       <c r="N21" t="n">
         <v>301</v>
       </c>
       <c r="O21" t="n">
-        <v>177.413191992497</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>301</v>
+        <v>122.8471736799054</v>
       </c>
       <c r="R21" t="n">
         <v>301</v>
@@ -29016,13 +29016,13 @@
         <v>301</v>
       </c>
       <c r="C22" t="n">
+        <v>297.4186397169557</v>
+      </c>
+      <c r="D22" t="n">
         <v>301</v>
       </c>
-      <c r="D22" t="n">
-        <v>285.5362180555555</v>
-      </c>
       <c r="E22" t="n">
-        <v>301</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F22" t="n">
         <v>301</v>
@@ -29031,13 +29031,13 @@
         <v>301</v>
       </c>
       <c r="H22" t="n">
-        <v>223.5765031507989</v>
+        <v>301</v>
       </c>
       <c r="I22" t="n">
         <v>301</v>
       </c>
       <c r="J22" t="n">
-        <v>301</v>
+        <v>128.1619208728401</v>
       </c>
       <c r="K22" t="n">
         <v>301</v>
@@ -29070,13 +29070,13 @@
         <v>301</v>
       </c>
       <c r="U22" t="n">
-        <v>150.9265224219989</v>
+        <v>301</v>
       </c>
       <c r="V22" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W22" t="n">
         <v>301</v>
-      </c>
-      <c r="W22" t="n">
-        <v>245.692532014615</v>
       </c>
       <c r="X22" t="n">
         <v>301</v>
@@ -29119,7 +29119,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>32.71319599894355</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -29137,10 +29137,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>32.16598080989746</v>
+        <v>64.87917680884104</v>
       </c>
       <c r="R23" t="n">
-        <v>297.1316448568214</v>
+        <v>297.1316448568211</v>
       </c>
       <c r="S23" t="n">
         <v>302</v>
@@ -29192,31 +29192,31 @@
         <v>302</v>
       </c>
       <c r="I24" t="n">
-        <v>210.8596281612361</v>
+        <v>302</v>
       </c>
       <c r="J24" t="n">
-        <v>242.4138338033203</v>
+        <v>58.37389038984335</v>
       </c>
       <c r="K24" t="n">
-        <v>198.2414050901468</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>208.1647782656032</v>
+        <v>302</v>
       </c>
       <c r="N24" t="n">
-        <v>169.5284298928841</v>
+        <v>302</v>
       </c>
       <c r="O24" t="n">
-        <v>181.413191992497</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>132.7638512081147</v>
+        <v>178.4062922315566</v>
       </c>
       <c r="Q24" t="n">
-        <v>101.3950642075979</v>
+        <v>302</v>
       </c>
       <c r="R24" t="n">
         <v>302</v>
@@ -29250,13 +29250,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>302</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C25" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D25" t="n">
-        <v>302</v>
+        <v>301.634279858014</v>
       </c>
       <c r="E25" t="n">
         <v>302</v>
@@ -29271,10 +29271,10 @@
         <v>302</v>
       </c>
       <c r="I25" t="n">
-        <v>282.3101821217581</v>
+        <v>302</v>
       </c>
       <c r="J25" t="n">
-        <v>128.1619208728401</v>
+        <v>302</v>
       </c>
       <c r="K25" t="n">
         <v>302</v>
@@ -29307,13 +29307,13 @@
         <v>302</v>
       </c>
       <c r="U25" t="n">
+        <v>150.9265224219989</v>
+      </c>
+      <c r="V25" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W25" t="n">
         <v>302</v>
-      </c>
-      <c r="V25" t="n">
-        <v>302</v>
-      </c>
-      <c r="W25" t="n">
-        <v>226.3728098387097</v>
       </c>
       <c r="X25" t="n">
         <v>302</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>255</v>
+        <v>118.3584095148163</v>
       </c>
       <c r="N26" t="n">
-        <v>241.5778467849456</v>
+        <v>244.8383852055136</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -29429,13 +29429,13 @@
         <v>255</v>
       </c>
       <c r="I27" t="n">
-        <v>193.132046268707</v>
+        <v>255</v>
       </c>
       <c r="J27" t="n">
-        <v>19.83866021378883</v>
+        <v>202.4138338033202</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>110.8177321686379</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -29444,16 +29444,16 @@
         <v>208.1647782656032</v>
       </c>
       <c r="N27" t="n">
-        <v>169.5284298928841</v>
+        <v>255</v>
       </c>
       <c r="O27" t="n">
-        <v>141.4131919924969</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>250.1198688640645</v>
+        <v>255</v>
       </c>
       <c r="R27" t="n">
         <v>255</v>
@@ -29511,7 +29511,7 @@
         <v>255</v>
       </c>
       <c r="J28" t="n">
-        <v>255</v>
+        <v>159.9616045736127</v>
       </c>
       <c r="K28" t="n">
         <v>255</v>
@@ -29614,7 +29614,7 @@
         <v>32.16598080989746</v>
       </c>
       <c r="R29" t="n">
-        <v>280.8823725951506</v>
+        <v>233.6823864121155</v>
       </c>
       <c r="S29" t="n">
         <v>313</v>
@@ -29666,31 +29666,31 @@
         <v>313</v>
       </c>
       <c r="I30" t="n">
-        <v>210.8596281612361</v>
+        <v>313</v>
       </c>
       <c r="J30" t="n">
-        <v>163.3613601788932</v>
+        <v>202.4138338033202</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>128.6807912997903</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>208.1647782656032</v>
       </c>
       <c r="N30" t="n">
-        <v>169.5284298928841</v>
+        <v>313</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>138.4062922315566</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>267.3950642075978</v>
+        <v>249.8177321686379</v>
       </c>
       <c r="R30" t="n">
         <v>313</v>
@@ -29727,28 +29727,28 @@
         <v>313</v>
       </c>
       <c r="C31" t="n">
-        <v>272.7252466480447</v>
+        <v>313</v>
       </c>
       <c r="D31" t="n">
-        <v>285.5362180555555</v>
+        <v>313</v>
       </c>
       <c r="E31" t="n">
-        <v>280.9809048369565</v>
+        <v>313</v>
       </c>
       <c r="F31" t="n">
-        <v>274.3828559677419</v>
+        <v>313</v>
       </c>
       <c r="G31" t="n">
-        <v>244.4596105464481</v>
+        <v>313</v>
       </c>
       <c r="H31" t="n">
         <v>313</v>
       </c>
       <c r="I31" t="n">
-        <v>313.0000000000007</v>
+        <v>313</v>
       </c>
       <c r="J31" t="n">
-        <v>67.75091000961481</v>
+        <v>128.1619208728401</v>
       </c>
       <c r="K31" t="n">
         <v>220.6401180634381</v>
@@ -29778,22 +29778,22 @@
         <v>313</v>
       </c>
       <c r="T31" t="n">
-        <v>207.5281730636348</v>
+        <v>313.0000000000007</v>
       </c>
       <c r="U31" t="n">
-        <v>313.0000000000007</v>
+        <v>223.3975166762014</v>
       </c>
       <c r="V31" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W31" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X31" t="n">
+        <v>247.4436454301076</v>
+      </c>
+      <c r="Y31" t="n">
         <v>313</v>
-      </c>
-      <c r="X31" t="n">
-        <v>313</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="32">
@@ -29851,7 +29851,7 @@
         <v>32.16598080989746</v>
       </c>
       <c r="R32" t="n">
-        <v>325</v>
+        <v>175.1175622915115</v>
       </c>
       <c r="S32" t="n">
         <v>325</v>
@@ -29903,10 +29903,10 @@
         <v>325</v>
       </c>
       <c r="I33" t="n">
-        <v>193.132046268707</v>
+        <v>210.8596281612361</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>202.4138338033202</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -29915,13 +29915,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
+        <v>280.7278180654072</v>
+      </c>
+      <c r="N33" t="n">
         <v>325</v>
       </c>
-      <c r="N33" t="n">
-        <v>169.5284298928841</v>
-      </c>
       <c r="O33" t="n">
-        <v>138.5690316649285</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -29964,16 +29964,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C34" t="n">
-        <v>303.9890000825416</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D34" t="n">
-        <v>285.5362180555555</v>
+        <v>325</v>
       </c>
       <c r="E34" t="n">
-        <v>280.9809048369565</v>
+        <v>325</v>
       </c>
       <c r="F34" t="n">
-        <v>325</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G34" t="n">
         <v>244.4596105464481</v>
@@ -29985,7 +29985,7 @@
         <v>325</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>261.9296942083752</v>
       </c>
       <c r="K34" t="n">
         <v>220.6401180634381</v>
@@ -30015,16 +30015,16 @@
         <v>325</v>
       </c>
       <c r="T34" t="n">
-        <v>207.5281730636348</v>
+        <v>325</v>
       </c>
       <c r="U34" t="n">
         <v>150.9265224219989</v>
       </c>
       <c r="V34" t="n">
-        <v>325</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W34" t="n">
-        <v>325</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X34" t="n">
         <v>325</v>
@@ -30076,7 +30076,7 @@
         <v>251.739461579432</v>
       </c>
       <c r="N35" t="n">
-        <v>127.1219283069222</v>
+        <v>244.8383852055136</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -30085,10 +30085,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>32.16598080989746</v>
       </c>
       <c r="R35" t="n">
-        <v>325</v>
+        <v>235.7848448805794</v>
       </c>
       <c r="S35" t="n">
         <v>325</v>
@@ -30140,10 +30140,10 @@
         <v>325</v>
       </c>
       <c r="I36" t="n">
-        <v>210.8596281612361</v>
+        <v>325</v>
       </c>
       <c r="J36" t="n">
-        <v>36.41383380332024</v>
+        <v>202.4138338033202</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -30155,13 +30155,13 @@
         <v>208.1647782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>325</v>
+        <v>169.5284298928841</v>
       </c>
       <c r="O36" t="n">
-        <v>100.1567475682473</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>138.4062922315566</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>267.3950642075978</v>
@@ -30198,10 +30198,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>287.1138003370787</v>
+        <v>325</v>
       </c>
       <c r="C37" t="n">
-        <v>325</v>
+        <v>322.4344045873603</v>
       </c>
       <c r="D37" t="n">
         <v>325</v>
@@ -30216,13 +30216,13 @@
         <v>325</v>
       </c>
       <c r="H37" t="n">
-        <v>223.5765031507989</v>
+        <v>325</v>
       </c>
       <c r="I37" t="n">
         <v>181.4093995055526</v>
       </c>
       <c r="J37" t="n">
-        <v>294.1619208728401</v>
+        <v>128.1619208728401</v>
       </c>
       <c r="K37" t="n">
         <v>220.6401180634381</v>
@@ -30252,16 +30252,16 @@
         <v>325</v>
       </c>
       <c r="T37" t="n">
-        <v>207.5281730636348</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>150.9265224219989</v>
       </c>
       <c r="V37" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W37" t="n">
         <v>325</v>
-      </c>
-      <c r="W37" t="n">
-        <v>287.3862382520641</v>
       </c>
       <c r="X37" t="n">
         <v>247.4436454301076</v>
@@ -30310,10 +30310,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>315.5523185970912</v>
+        <v>251.739461579432</v>
       </c>
       <c r="N38" t="n">
-        <v>181.0255281878544</v>
+        <v>244.8383852055136</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -30380,28 +30380,28 @@
         <v>210.8596281612361</v>
       </c>
       <c r="J39" t="n">
-        <v>36.41383380332024</v>
+        <v>202.4138338033202</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>38.97808145659378</v>
+        <v>7.855943795268523</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="N39" t="n">
-        <v>324</v>
+        <v>169.5284298928841</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>138.4062922315566</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>267.3950642075978</v>
+        <v>101.3950642075979</v>
       </c>
       <c r="R39" t="n">
         <v>324</v>
@@ -30435,13 +30435,13 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C40" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D40" t="n">
         <v>324</v>
-      </c>
-      <c r="C40" t="n">
-        <v>324</v>
-      </c>
-      <c r="D40" t="n">
-        <v>285.5362180555555</v>
       </c>
       <c r="E40" t="n">
         <v>324</v>
@@ -30450,16 +30450,16 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
-        <v>324</v>
+        <v>244.4596105464481</v>
       </c>
       <c r="H40" t="n">
         <v>324</v>
       </c>
       <c r="I40" t="n">
-        <v>181.4093995055526</v>
+        <v>324</v>
       </c>
       <c r="J40" t="n">
-        <v>294.1619208728401</v>
+        <v>238.5009957695588</v>
       </c>
       <c r="K40" t="n">
         <v>220.6401180634381</v>
@@ -30489,19 +30489,19 @@
         <v>324</v>
       </c>
       <c r="T40" t="n">
-        <v>311.1208133059985</v>
+        <v>207.5281730636348</v>
       </c>
       <c r="U40" t="n">
         <v>150.9265224219989</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>324</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>324</v>
       </c>
       <c r="X40" t="n">
-        <v>324</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
         <v>287.4653528494624</v>
@@ -30547,7 +30547,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -30620,22 +30620,22 @@
         <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>13.4493117167563</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.185160773360072</v>
       </c>
       <c r="Q42" t="n">
         <v>100</v>
@@ -30784,10 +30784,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>12.02010050251256</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -30796,7 +30796,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>13</v>
@@ -30854,25 +30854,25 @@
         <v>13</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>6.377358490566038</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q45" t="n">
         <v>13</v>
@@ -34834,10 +34834,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>134.4360014556385</v>
       </c>
       <c r="O3" t="n">
-        <v>159.0228094631416</v>
+        <v>24.58680800750304</v>
       </c>
       <c r="P3" t="n">
         <v>27.59370776844339</v>
@@ -34886,16 +34886,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.5403894535519</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>43.30768198627548</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -34931,10 +34931,10 @@
         <v>47.80861865780031</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="V4" t="n">
         <v>166</v>
@@ -34943,7 +34943,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>111.484310635129</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -35059,7 +35059,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>134.4360014556385</v>
       </c>
       <c r="K6" t="n">
         <v>7.758594909853286</v>
@@ -35077,7 +35077,7 @@
         <v>24.58680800750304</v>
       </c>
       <c r="P6" t="n">
-        <v>162.0297092240818</v>
+        <v>27.59370776844339</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35117,16 +35117,16 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -35138,13 +35138,13 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>29.13007909473213</v>
+        <v>166</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>63.31624069467985</v>
+        <v>17.64909917056464</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>47.8086186578003</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -35177,13 +35177,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35308,10 +35308,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>134.4360014556385</v>
       </c>
       <c r="O9" t="n">
-        <v>159.0228094631416</v>
+        <v>24.58680800750304</v>
       </c>
       <c r="P9" t="n">
         <v>27.59370776844339</v>
@@ -35351,16 +35351,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>5.908860902193001</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -35372,16 +35372,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>63.31624069467983</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35411,13 +35411,13 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>25.54333498112794</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -35530,25 +35530,25 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>60.14037183876391</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="K12" t="n">
-        <v>166</v>
+        <v>11.34604113649652</v>
       </c>
       <c r="L12" t="n">
-        <v>131.6992215244858</v>
+        <v>37.31920870020967</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>62.83522173439684</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>101.4715701071159</v>
       </c>
       <c r="O12" t="n">
-        <v>166</v>
+        <v>24.58680800750304</v>
       </c>
       <c r="P12" t="n">
         <v>27.59370776844339</v>
@@ -35767,22 +35767,22 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.544791089879328</v>
+        <v>89.14037183876391</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>166</v>
+        <v>7.758594909853286</v>
       </c>
       <c r="L15" t="n">
         <v>37.31920870020967</v>
       </c>
       <c r="M15" t="n">
-        <v>91.83522173439684</v>
+        <v>33.00947596854308</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>130.4715701071159</v>
       </c>
       <c r="O15" t="n">
         <v>166</v>
@@ -35831,13 +35831,13 @@
         <v>27.27475335195533</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>19.01909516304346</v>
       </c>
       <c r="F16" t="n">
-        <v>25.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>55.54038945355194</v>
@@ -35849,10 +35849,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4.471857082885183</v>
+        <v>74.01395263212437</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35882,7 +35882,7 @@
         <v>92.47182693636523</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>149.0734775780011</v>
       </c>
       <c r="V16" t="n">
         <v>100.8296897837838</v>
@@ -35894,7 +35894,7 @@
         <v>52.55635456989245</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -36004,31 +36004,31 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>90.14037183876391</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="K18" t="n">
-        <v>182</v>
+        <v>7.758594909853286</v>
       </c>
       <c r="L18" t="n">
-        <v>54.21753514362433</v>
+        <v>37.31920870020967</v>
       </c>
       <c r="M18" t="n">
         <v>92.83522173439684</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>131.4715701071159</v>
       </c>
       <c r="O18" t="n">
-        <v>182</v>
+        <v>24.58680800750304</v>
       </c>
       <c r="P18" t="n">
         <v>27.59370776844339</v>
       </c>
       <c r="Q18" t="n">
-        <v>182</v>
+        <v>126.9409815801785</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36065,7 +36065,7 @@
         <v>13.88619966292134</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>28.27475335195533</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -36074,22 +36074,22 @@
         <v>20.01909516304346</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>26.61714403225807</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>56.54038945355194</v>
       </c>
       <c r="H19" t="n">
         <v>77.42349684920106</v>
       </c>
       <c r="I19" t="n">
-        <v>119.5906004944474</v>
+        <v>23.9041449534664</v>
       </c>
       <c r="J19" t="n">
-        <v>172.8380791271599</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>80.35988193656186</v>
+        <v>80.35988193656189</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36116,16 +36116,16 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>67.60841990891566</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>150.0734775780011</v>
       </c>
       <c r="V19" t="n">
         <v>101.8296897837838</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>74.62719016129032</v>
       </c>
       <c r="X19" t="n">
         <v>53.55635456989245</v>
@@ -36162,7 +36162,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>31.37951398073869</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>75.50611938305039</v>
@@ -36186,7 +36186,7 @@
         <v>187.0158746326854</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>31.37951398073898</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36241,10 +36241,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>90.14037183876391</v>
       </c>
       <c r="J21" t="n">
-        <v>29.40957526056907</v>
+        <v>202.0000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>7.758594909853286</v>
@@ -36253,19 +36253,19 @@
         <v>202.0000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>92.83522173439684</v>
       </c>
       <c r="N21" t="n">
         <v>131.4715701071159</v>
       </c>
       <c r="O21" t="n">
-        <v>202.0000000000001</v>
+        <v>24.58680800750304</v>
       </c>
       <c r="P21" t="n">
         <v>27.59370776844339</v>
       </c>
       <c r="Q21" t="n">
-        <v>199.6049357924022</v>
+        <v>21.45210947230749</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36302,13 +36302,13 @@
         <v>13.88619966292134</v>
       </c>
       <c r="C22" t="n">
-        <v>28.27475335195533</v>
+        <v>24.69339306891105</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>15.46378194444452</v>
       </c>
       <c r="E22" t="n">
-        <v>20.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>26.61714403225807</v>
@@ -36317,13 +36317,13 @@
         <v>56.54038945355194</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>77.42349684920106</v>
       </c>
       <c r="I22" t="n">
         <v>119.5906004944474</v>
       </c>
       <c r="J22" t="n">
-        <v>172.8380791271599</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>80.35988193656186</v>
@@ -36356,13 +36356,13 @@
         <v>93.47182693636523</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>150.0734775780011</v>
       </c>
       <c r="V22" t="n">
-        <v>101.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>19.31972217590536</v>
+        <v>74.62719016129032</v>
       </c>
       <c r="X22" t="n">
         <v>53.55635456989245</v>
@@ -36405,7 +36405,7 @@
         <v>75.50611938305039</v>
       </c>
       <c r="K23" t="n">
-        <v>198.3976784110039</v>
+        <v>165.6844824120603</v>
       </c>
       <c r="L23" t="n">
         <v>205.5462512562814</v>
@@ -36423,7 +36423,7 @@
         <v>187.0158746326854</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>32.71319599894358</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36478,31 +36478,31 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>91.14037183876391</v>
       </c>
       <c r="J24" t="n">
-        <v>206.0000000000001</v>
+        <v>21.96005658652311</v>
       </c>
       <c r="K24" t="n">
-        <v>206.0000000000001</v>
+        <v>7.758594909853286</v>
       </c>
       <c r="L24" t="n">
         <v>37.31920870020967</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>93.83522173439684</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>132.4715701071159</v>
       </c>
       <c r="O24" t="n">
+        <v>24.58680800750304</v>
+      </c>
+      <c r="P24" t="n">
         <v>206.0000000000001</v>
       </c>
-      <c r="P24" t="n">
-        <v>160.357558976558</v>
-      </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>200.6049357924022</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36536,13 +36536,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>16.46378194444452</v>
+        <v>16.09806180245849</v>
       </c>
       <c r="E25" t="n">
         <v>21.01909516304346</v>
@@ -36557,10 +36557,10 @@
         <v>78.42349684920106</v>
       </c>
       <c r="I25" t="n">
-        <v>100.9007826162055</v>
+        <v>120.5906004944474</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>173.8380791271599</v>
       </c>
       <c r="K25" t="n">
         <v>81.35988193656186</v>
@@ -36593,13 +36593,13 @@
         <v>94.47182693636523</v>
       </c>
       <c r="U25" t="n">
-        <v>151.0734775780011</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>102.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>75.62719016129032</v>
       </c>
       <c r="X25" t="n">
         <v>54.55635456989245</v>
@@ -36715,13 +36715,13 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>44.1403718387639</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="K27" t="n">
-        <v>121.9737205927196</v>
+        <v>118.5763270784912</v>
       </c>
       <c r="L27" t="n">
         <v>37.31920870020967</v>
@@ -36730,16 +36730,16 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>85.47157010711589</v>
       </c>
       <c r="O27" t="n">
-        <v>166</v>
+        <v>24.58680800750304</v>
       </c>
       <c r="P27" t="n">
-        <v>166</v>
+        <v>27.59370776844339</v>
       </c>
       <c r="Q27" t="n">
-        <v>166</v>
+        <v>153.6049357924022</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36952,31 +36952,31 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>102.1403718387639</v>
       </c>
       <c r="J30" t="n">
-        <v>126.9475263755729</v>
+        <v>166</v>
       </c>
       <c r="K30" t="n">
         <v>7.758594909853286</v>
       </c>
       <c r="L30" t="n">
-        <v>166</v>
+        <v>37.31920870020967</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>143.4715701071159</v>
       </c>
       <c r="O30" t="n">
         <v>24.58680800750304</v>
       </c>
       <c r="P30" t="n">
-        <v>166</v>
+        <v>27.59370776844339</v>
       </c>
       <c r="Q30" t="n">
-        <v>166</v>
+        <v>148.42266796104</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37013,28 +37013,28 @@
         <v>25.88619966292134</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>40.27475335195533</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>27.46378194444452</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>32.01909516304346</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>38.61714403225807</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>68.54038945355194</v>
       </c>
       <c r="H31" t="n">
         <v>89.42349684920106</v>
       </c>
       <c r="I31" t="n">
-        <v>153.9369050356202</v>
+        <v>131.5906004944474</v>
       </c>
       <c r="J31" t="n">
-        <v>73.7893054360021</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -37064,22 +37064,22 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>105.471826936366</v>
       </c>
       <c r="U31" t="n">
-        <v>162.0734775780018</v>
+        <v>72.47099425420244</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>86.62719016129032</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>65.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>25.53464715053764</v>
       </c>
     </row>
     <row r="32">
@@ -37192,7 +37192,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>138.6303565075945</v>
+        <v>166</v>
       </c>
       <c r="K33" t="n">
         <v>7.758594909853286</v>
@@ -37201,13 +37201,13 @@
         <v>37.31920870020967</v>
       </c>
       <c r="M33" t="n">
-        <v>116.8352217343968</v>
+        <v>72.56303979980403</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>155.4715701071159</v>
       </c>
       <c r="O33" t="n">
-        <v>163.1558396724315</v>
+        <v>24.58680800750304</v>
       </c>
       <c r="P33" t="n">
         <v>27.59370776844339</v>
@@ -37250,16 +37250,16 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>31.2637534344969</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>39.46378194444452</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>44.01909516304346</v>
       </c>
       <c r="F34" t="n">
-        <v>50.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -37268,10 +37268,10 @@
         <v>101.4234968492011</v>
       </c>
       <c r="I34" t="n">
-        <v>165.9369050356194</v>
+        <v>143.5906004944474</v>
       </c>
       <c r="J34" t="n">
-        <v>6.038395426387297</v>
+        <v>133.7677733355351</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -37301,16 +37301,16 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>117.4718269363652</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>125.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>98.62719016129032</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>77.55635456989245</v>
@@ -37426,10 +37426,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>114.1403718387639</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="K36" t="n">
         <v>7.758594909853286</v>
@@ -37441,13 +37441,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>155.4715701071159</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>124.7435555757504</v>
+        <v>24.58680800750304</v>
       </c>
       <c r="P36" t="n">
-        <v>166</v>
+        <v>141.4879458365994</v>
       </c>
       <c r="Q36" t="n">
         <v>166</v>
@@ -37484,10 +37484,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>37.88619966292134</v>
       </c>
       <c r="C37" t="n">
-        <v>52.27475335195533</v>
+        <v>49.70915793931567</v>
       </c>
       <c r="D37" t="n">
         <v>39.46378194444452</v>
@@ -37502,13 +37502,13 @@
         <v>80.54038945355194</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>101.4234968492011</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -37538,16 +37538,16 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>117.4718269363652</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>125.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>61.01342841335445</v>
+        <v>98.62719016129032</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -37666,28 +37666,28 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="K39" t="n">
-        <v>7.758594909853286</v>
+        <v>166</v>
       </c>
       <c r="L39" t="n">
-        <v>76.29729015680346</v>
+        <v>45.17515249547819</v>
       </c>
       <c r="M39" t="n">
-        <v>62.17866611165351</v>
+        <v>115.8352217343968</v>
       </c>
       <c r="N39" t="n">
-        <v>154.4715701071159</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>24.58680800750304</v>
       </c>
       <c r="P39" t="n">
-        <v>166</v>
+        <v>139.6957470555512</v>
       </c>
       <c r="Q39" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37721,13 +37721,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>36.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>51.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>38.46378194444452</v>
       </c>
       <c r="E40" t="n">
         <v>43.01909516304346</v>
@@ -37736,16 +37736,16 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>79.54038945355194</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>100.4234968492011</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>142.5906004944474</v>
       </c>
       <c r="J40" t="n">
-        <v>166</v>
+        <v>110.3390748967187</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -37775,19 +37775,19 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>103.5926402423637</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>124.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>97.62719016129032</v>
       </c>
       <c r="X40" t="n">
-        <v>76.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -37906,25 +37906,25 @@
         <v>63.58616619667976</v>
       </c>
       <c r="K42" t="n">
+        <v>107.7585949098533</v>
+      </c>
+      <c r="L42" t="n">
+        <v>137.3192087002097</v>
+      </c>
+      <c r="M42" t="n">
+        <v>66.02961644740915</v>
+      </c>
+      <c r="N42" t="n">
         <v>150</v>
       </c>
-      <c r="L42" t="n">
-        <v>37.31920870020967</v>
-      </c>
-      <c r="M42" t="n">
-        <v>150</v>
-      </c>
-      <c r="N42" t="n">
-        <v>15.44031127406116</v>
-      </c>
       <c r="O42" t="n">
-        <v>150</v>
+        <v>24.58680800750304</v>
       </c>
       <c r="P42" t="n">
-        <v>27.59370776844339</v>
+        <v>28.77886854180347</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>15.88013113593552</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -38140,25 +38140,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>25.80836406167507</v>
       </c>
       <c r="K45" t="n">
-        <v>130</v>
+        <v>20.75859490985329</v>
       </c>
       <c r="L45" t="n">
         <v>130</v>
       </c>
       <c r="M45" t="n">
-        <v>72.56695897152839</v>
+        <v>130</v>
       </c>
       <c r="N45" t="n">
         <v>130</v>
       </c>
       <c r="O45" t="n">
-        <v>24.58680800750304</v>
+        <v>37.58680800750304</v>
       </c>
       <c r="P45" t="n">
-        <v>27.59370776844339</v>
+        <v>40.59370776844339</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
